--- a/research/traditional_assets/database/data/jordan/jordan_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_electrical_equipment.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1463373230679572</v>
+        <v>0.1460806484218213</v>
       </c>
       <c r="C2">
-        <v>37.86797128153904</v>
+        <v>37.58776808677675</v>
       </c>
       <c r="D2">
-        <v>35.70797128153905</v>
+        <v>35.79936808677675</v>
       </c>
       <c r="E2">
-        <v>-8.56</v>
+        <v>-8.1884</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3716</v>
       </c>
       <c r="G2">
         <v>2.16</v>
@@ -1445,28 +1445,28 @@
         <v>3.64</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01869148</v>
       </c>
       <c r="N2">
-        <v>3.64</v>
+        <v>3.62130852</v>
       </c>
       <c r="O2">
-        <v>0.7280000000000001</v>
+        <v>0.724261704</v>
       </c>
       <c r="P2">
-        <v>2.912</v>
+        <v>2.897046816</v>
       </c>
       <c r="Q2">
-        <v>5.002000000000001</v>
+        <v>4.987046816</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1463373230679572</v>
+        <v>0.1471497458806276</v>
       </c>
       <c r="T2">
-        <v>1.100924895422504</v>
+        <v>1.109821258213797</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>194.7411333933964</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1460806484218213</v>
+        <v>0.1458239737756854</v>
       </c>
       <c r="C3">
-        <v>37.58776808677675</v>
+        <v>37.30803396441294</v>
       </c>
       <c r="D3">
-        <v>35.79936808677675</v>
+        <v>35.89123396441294</v>
       </c>
       <c r="E3">
-        <v>-8.1884</v>
+        <v>-7.816800000000001</v>
       </c>
       <c r="F3">
-        <v>0.3716</v>
+        <v>0.7432000000000001</v>
       </c>
       <c r="G3">
         <v>2.16</v>
@@ -1527,28 +1527,28 @@
         <v>3.64</v>
       </c>
       <c r="M3">
-        <v>0.01869148</v>
+        <v>0.03738296</v>
       </c>
       <c r="N3">
-        <v>3.62130852</v>
+        <v>3.60261704</v>
       </c>
       <c r="O3">
-        <v>0.724261704</v>
+        <v>0.720523408</v>
       </c>
       <c r="P3">
-        <v>2.897046816</v>
+        <v>2.882093632</v>
       </c>
       <c r="Q3">
-        <v>4.987046816</v>
+        <v>4.972093632</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1471497458806276</v>
+        <v>0.1479787487506994</v>
       </c>
       <c r="T3">
-        <v>1.109821258213797</v>
+        <v>1.118899179429402</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>194.7411333933964</v>
+        <v>97.37056669669818</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1458239737756854</v>
+        <v>0.1455672991295495</v>
       </c>
       <c r="C4">
-        <v>37.30803396441294</v>
+        <v>37.02877253484206</v>
       </c>
       <c r="D4">
-        <v>35.89123396441294</v>
+        <v>35.98357253484207</v>
       </c>
       <c r="E4">
-        <v>-7.816800000000001</v>
+        <v>-7.445200000000001</v>
       </c>
       <c r="F4">
-        <v>0.7432000000000001</v>
+        <v>1.1148</v>
       </c>
       <c r="G4">
         <v>2.16</v>
@@ -1609,28 +1609,28 @@
         <v>3.64</v>
       </c>
       <c r="M4">
-        <v>0.03738296</v>
+        <v>0.05607444</v>
       </c>
       <c r="N4">
-        <v>3.60261704</v>
+        <v>3.58392556</v>
       </c>
       <c r="O4">
-        <v>0.720523408</v>
+        <v>0.7167851120000001</v>
       </c>
       <c r="P4">
-        <v>2.882093632</v>
+        <v>2.867140448</v>
       </c>
       <c r="Q4">
-        <v>4.972093632</v>
+        <v>4.957140448000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1479787487506994</v>
+        <v>0.1488248444634531</v>
       </c>
       <c r="T4">
-        <v>1.118899179429402</v>
+        <v>1.128164274278319</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>97.37056669669818</v>
+        <v>64.91371113113212</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1455672991295495</v>
+        <v>0.1453106244834136</v>
       </c>
       <c r="C5">
-        <v>37.02877253484206</v>
+        <v>36.74998745581189</v>
       </c>
       <c r="D5">
-        <v>35.98357253484207</v>
+        <v>36.0763874558119</v>
       </c>
       <c r="E5">
-        <v>-7.445200000000001</v>
+        <v>-7.073600000000001</v>
       </c>
       <c r="F5">
-        <v>1.1148</v>
+        <v>1.4864</v>
       </c>
       <c r="G5">
         <v>2.16</v>
@@ -1691,28 +1691,28 @@
         <v>3.64</v>
       </c>
       <c r="M5">
-        <v>0.05607444</v>
+        <v>0.07476592</v>
       </c>
       <c r="N5">
-        <v>3.58392556</v>
+        <v>3.56523408</v>
       </c>
       <c r="O5">
-        <v>0.7167851120000001</v>
+        <v>0.7130468160000001</v>
       </c>
       <c r="P5">
-        <v>2.867140448</v>
+        <v>2.852187264</v>
       </c>
       <c r="Q5">
-        <v>4.957140448000001</v>
+        <v>4.942187264000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1488248444634531</v>
+        <v>0.1496885671702225</v>
       </c>
       <c r="T5">
-        <v>1.128164274278319</v>
+        <v>1.137622391936588</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>64.91371113113212</v>
+        <v>48.68528334834909</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1453106244834136</v>
+        <v>0.1450539498372777</v>
       </c>
       <c r="C6">
-        <v>36.74998745581189</v>
+        <v>36.47168242290655</v>
       </c>
       <c r="D6">
-        <v>36.0763874558119</v>
+        <v>36.16968242290654</v>
       </c>
       <c r="E6">
-        <v>-7.073600000000001</v>
+        <v>-6.702</v>
       </c>
       <c r="F6">
-        <v>1.4864</v>
+        <v>1.858</v>
       </c>
       <c r="G6">
         <v>2.16</v>
@@ -1773,28 +1773,28 @@
         <v>3.64</v>
       </c>
       <c r="M6">
-        <v>0.07476592</v>
+        <v>0.09345740000000001</v>
       </c>
       <c r="N6">
-        <v>3.56523408</v>
+        <v>3.5465426</v>
       </c>
       <c r="O6">
-        <v>0.7130468160000001</v>
+        <v>0.70930852</v>
       </c>
       <c r="P6">
-        <v>2.852187264</v>
+        <v>2.83723408</v>
       </c>
       <c r="Q6">
-        <v>4.942187264000001</v>
+        <v>4.92723408</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1496885671702225</v>
+        <v>0.1505704735129239</v>
       </c>
       <c r="T6">
-        <v>1.137622391936588</v>
+        <v>1.147279627861347</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.68528334834909</v>
+        <v>38.94822667867927</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1450539498372777</v>
+        <v>0.1447972751911417</v>
       </c>
       <c r="C7">
-        <v>36.47168242290655</v>
+        <v>36.19386117003693</v>
       </c>
       <c r="D7">
-        <v>36.16968242290654</v>
+        <v>36.26346117003693</v>
       </c>
       <c r="E7">
-        <v>-6.702</v>
+        <v>-6.3304</v>
       </c>
       <c r="F7">
-        <v>1.858</v>
+        <v>2.2296</v>
       </c>
       <c r="G7">
         <v>2.16</v>
@@ -1855,28 +1855,28 @@
         <v>3.64</v>
       </c>
       <c r="M7">
-        <v>0.09345740000000001</v>
+        <v>0.11214888</v>
       </c>
       <c r="N7">
-        <v>3.5465426</v>
+        <v>3.52785112</v>
       </c>
       <c r="O7">
-        <v>0.70930852</v>
+        <v>0.7055702240000001</v>
       </c>
       <c r="P7">
-        <v>2.83723408</v>
+        <v>2.822280896</v>
       </c>
       <c r="Q7">
-        <v>4.92723408</v>
+        <v>4.912280896</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1505704735129239</v>
+        <v>0.1514711438203636</v>
       </c>
       <c r="T7">
-        <v>1.147279627861347</v>
+        <v>1.157142336890888</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.94822667867927</v>
+        <v>32.45685556556606</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1447972751911417</v>
+        <v>0.1445406005450059</v>
       </c>
       <c r="C8">
-        <v>36.19386117003693</v>
+        <v>35.91652746993895</v>
       </c>
       <c r="D8">
-        <v>36.26346117003693</v>
+        <v>36.35772746993895</v>
       </c>
       <c r="E8">
-        <v>-6.330400000000001</v>
+        <v>-5.9588</v>
       </c>
       <c r="F8">
-        <v>2.2296</v>
+        <v>2.6012</v>
       </c>
       <c r="G8">
         <v>2.16</v>
@@ -1937,28 +1937,28 @@
         <v>3.64</v>
       </c>
       <c r="M8">
-        <v>0.11214888</v>
+        <v>0.13084036</v>
       </c>
       <c r="N8">
-        <v>3.52785112</v>
+        <v>3.50915964</v>
       </c>
       <c r="O8">
-        <v>0.7055702240000001</v>
+        <v>0.701831928</v>
       </c>
       <c r="P8">
-        <v>2.822280896</v>
+        <v>2.807327712</v>
       </c>
       <c r="Q8">
-        <v>4.912280896</v>
+        <v>4.897327712000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1514711438203636</v>
+        <v>0.1523911833817267</v>
       </c>
       <c r="T8">
-        <v>1.157142336890888</v>
+        <v>1.167217147189881</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.45685556556606</v>
+        <v>27.82016191334234</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1445406005450058</v>
+        <v>0.1442839258988699</v>
       </c>
       <c r="C9">
-        <v>35.91652746993896</v>
+        <v>35.63968513467946</v>
       </c>
       <c r="D9">
-        <v>36.35772746993896</v>
+        <v>36.45248513467946</v>
       </c>
       <c r="E9">
-        <v>-5.9588</v>
+        <v>-5.5872</v>
       </c>
       <c r="F9">
-        <v>2.6012</v>
+        <v>2.9728</v>
       </c>
       <c r="G9">
         <v>2.16</v>
@@ -2019,28 +2019,28 @@
         <v>3.64</v>
       </c>
       <c r="M9">
-        <v>0.13084036</v>
+        <v>0.14953184</v>
       </c>
       <c r="N9">
-        <v>3.50915964</v>
+        <v>3.49046816</v>
       </c>
       <c r="O9">
-        <v>0.701831928</v>
+        <v>0.6980936320000001</v>
       </c>
       <c r="P9">
-        <v>2.807327712</v>
+        <v>2.792374528</v>
       </c>
       <c r="Q9">
-        <v>4.897327712000001</v>
+        <v>4.882374528000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1523911833817267</v>
+        <v>0.1533312238031195</v>
       </c>
       <c r="T9">
-        <v>1.167217147189881</v>
+        <v>1.17751097510407</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.82016191334233</v>
+        <v>24.34264167417454</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1442839258988699</v>
+        <v>0.144027251252734</v>
       </c>
       <c r="C10">
-        <v>35.63968513467946</v>
+        <v>35.36333801617001</v>
       </c>
       <c r="D10">
-        <v>36.45248513467946</v>
+        <v>36.54773801617001</v>
       </c>
       <c r="E10">
-        <v>-5.5872</v>
+        <v>-5.2156</v>
       </c>
       <c r="F10">
-        <v>2.9728</v>
+        <v>3.3444</v>
       </c>
       <c r="G10">
         <v>2.16</v>
@@ -2101,28 +2101,28 @@
         <v>3.64</v>
       </c>
       <c r="M10">
-        <v>0.14953184</v>
+        <v>0.16822332</v>
       </c>
       <c r="N10">
-        <v>3.49046816</v>
+        <v>3.47177668</v>
       </c>
       <c r="O10">
-        <v>0.6980936320000001</v>
+        <v>0.6943553360000001</v>
       </c>
       <c r="P10">
-        <v>2.792374528</v>
+        <v>2.777421344</v>
       </c>
       <c r="Q10">
-        <v>4.882374528000001</v>
+        <v>4.867421344</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1533312238031195</v>
+        <v>0.1542919244535538</v>
       </c>
       <c r="T10">
-        <v>1.17751097510407</v>
+        <v>1.188031040994395</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.34264167417454</v>
+        <v>21.63790371037737</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.144027251252734</v>
+        <v>0.1437705766065981</v>
       </c>
       <c r="C11">
-        <v>35.36333801617001</v>
+        <v>35.08749000668893</v>
       </c>
       <c r="D11">
-        <v>36.54773801617001</v>
+        <v>36.64349000668893</v>
       </c>
       <c r="E11">
-        <v>-5.2156</v>
+        <v>-4.844</v>
       </c>
       <c r="F11">
-        <v>3.3444</v>
+        <v>3.716</v>
       </c>
       <c r="G11">
         <v>2.16</v>
@@ -2183,28 +2183,28 @@
         <v>3.64</v>
       </c>
       <c r="M11">
-        <v>0.16822332</v>
+        <v>0.1869148</v>
       </c>
       <c r="N11">
-        <v>3.47177668</v>
+        <v>3.4530852</v>
       </c>
       <c r="O11">
-        <v>0.6943553360000001</v>
+        <v>0.6906170400000001</v>
       </c>
       <c r="P11">
-        <v>2.777421344</v>
+        <v>2.76246816</v>
       </c>
       <c r="Q11">
-        <v>4.867421344</v>
+        <v>4.852468160000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1542919244535538</v>
+        <v>0.1552739740073312</v>
       </c>
       <c r="T11">
-        <v>1.188031040994395</v>
+        <v>1.198784886126727</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.63790371037737</v>
+        <v>19.47411333933964</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1437705766065981</v>
+        <v>0.1435139019604622</v>
       </c>
       <c r="C12">
-        <v>35.08749000668892</v>
+        <v>34.81214503941147</v>
       </c>
       <c r="D12">
-        <v>36.64349000668891</v>
+        <v>36.73974503941147</v>
       </c>
       <c r="E12">
-        <v>-4.843999999999999</v>
+        <v>-4.4724</v>
       </c>
       <c r="F12">
-        <v>3.716000000000001</v>
+        <v>4.0876</v>
       </c>
       <c r="G12">
         <v>2.16</v>
@@ -2265,28 +2265,28 @@
         <v>3.64</v>
       </c>
       <c r="M12">
-        <v>0.1869148</v>
+        <v>0.20560628</v>
       </c>
       <c r="N12">
-        <v>3.4530852</v>
+        <v>3.43439372</v>
       </c>
       <c r="O12">
-        <v>0.6906170400000001</v>
+        <v>0.686878744</v>
       </c>
       <c r="P12">
-        <v>2.76246816</v>
+        <v>2.747514976</v>
       </c>
       <c r="Q12">
-        <v>4.852468160000001</v>
+        <v>4.837514976</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1552739740073312</v>
+        <v>0.1562780920904069</v>
       </c>
       <c r="T12">
-        <v>1.198784886126727</v>
+        <v>1.209780390700235</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.47411333933963</v>
+        <v>17.70373939939967</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1435139019604622</v>
+        <v>0.1432572273143262</v>
       </c>
       <c r="C13">
-        <v>34.81214503941147</v>
+        <v>34.53730708894833</v>
       </c>
       <c r="D13">
-        <v>36.73974503941147</v>
+        <v>36.83650708894834</v>
       </c>
       <c r="E13">
-        <v>-4.4724</v>
+        <v>-4.1008</v>
       </c>
       <c r="F13">
-        <v>4.0876</v>
+        <v>4.4592</v>
       </c>
       <c r="G13">
         <v>2.16</v>
@@ -2347,28 +2347,28 @@
         <v>3.64</v>
       </c>
       <c r="M13">
-        <v>0.20560628</v>
+        <v>0.22429776</v>
       </c>
       <c r="N13">
-        <v>3.43439372</v>
+        <v>3.41570224</v>
       </c>
       <c r="O13">
-        <v>0.686878744</v>
+        <v>0.6831404480000001</v>
       </c>
       <c r="P13">
-        <v>2.747514976</v>
+        <v>2.732561792</v>
       </c>
       <c r="Q13">
-        <v>4.837514976</v>
+        <v>4.822561792</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1562780920904069</v>
+        <v>0.1573050310390071</v>
       </c>
       <c r="T13">
-        <v>1.209780390700235</v>
+        <v>1.22102579310496</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.70373939939967</v>
+        <v>16.22842778278303</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1432572273143262</v>
+        <v>0.1430005526681903</v>
       </c>
       <c r="C14">
-        <v>34.53730708894833</v>
+        <v>34.2629801718928</v>
       </c>
       <c r="D14">
-        <v>36.83650708894834</v>
+        <v>36.9337801718928</v>
       </c>
       <c r="E14">
-        <v>-4.1008</v>
+        <v>-3.7292</v>
       </c>
       <c r="F14">
-        <v>4.4592</v>
+        <v>4.830800000000001</v>
       </c>
       <c r="G14">
         <v>2.16</v>
@@ -2429,28 +2429,28 @@
         <v>3.64</v>
       </c>
       <c r="M14">
-        <v>0.22429776</v>
+        <v>0.24298924</v>
       </c>
       <c r="N14">
-        <v>3.41570224</v>
+        <v>3.39701076</v>
       </c>
       <c r="O14">
-        <v>0.6831404480000001</v>
+        <v>0.6794021520000001</v>
       </c>
       <c r="P14">
-        <v>2.732561792</v>
+        <v>2.717608608</v>
       </c>
       <c r="Q14">
-        <v>4.822561792</v>
+        <v>4.807608608000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1573050310390071</v>
+        <v>0.1583555777795291</v>
       </c>
       <c r="T14">
-        <v>1.22102579310496</v>
+        <v>1.232529710507493</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.22842778278303</v>
+        <v>14.98008718410741</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1430005526681903</v>
+        <v>0.1427438780220544</v>
       </c>
       <c r="C15">
-        <v>34.2629801718928</v>
+        <v>33.98916834737641</v>
       </c>
       <c r="D15">
-        <v>36.9337801718928</v>
+        <v>37.03156834737641</v>
       </c>
       <c r="E15">
-        <v>-3.7292</v>
+        <v>-3.3576</v>
       </c>
       <c r="F15">
-        <v>4.830800000000001</v>
+        <v>5.202400000000001</v>
       </c>
       <c r="G15">
         <v>2.16</v>
@@ -2511,28 +2511,28 @@
         <v>3.64</v>
       </c>
       <c r="M15">
-        <v>0.24298924</v>
+        <v>0.26168072</v>
       </c>
       <c r="N15">
-        <v>3.39701076</v>
+        <v>3.37831928</v>
       </c>
       <c r="O15">
-        <v>0.6794021520000001</v>
+        <v>0.675663856</v>
       </c>
       <c r="P15">
-        <v>2.717608608</v>
+        <v>2.702655424</v>
       </c>
       <c r="Q15">
-        <v>4.807608608000001</v>
+        <v>4.792655424</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1583555777795291</v>
+        <v>0.1594305558395982</v>
       </c>
       <c r="T15">
-        <v>1.232529710507493</v>
+        <v>1.244301160872877</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.98008718410741</v>
+        <v>13.91008095667117</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1427438780220544</v>
+        <v>0.1424872033759185</v>
       </c>
       <c r="C16">
-        <v>33.98916834737641</v>
+        <v>33.71587571763372</v>
       </c>
       <c r="D16">
-        <v>37.03156834737641</v>
+        <v>37.12987571763372</v>
       </c>
       <c r="E16">
-        <v>-3.3576</v>
+        <v>-2.985999999999999</v>
       </c>
       <c r="F16">
-        <v>5.202400000000001</v>
+        <v>5.574000000000002</v>
       </c>
       <c r="G16">
         <v>2.16</v>
@@ -2593,28 +2593,28 @@
         <v>3.64</v>
       </c>
       <c r="M16">
-        <v>0.26168072</v>
+        <v>0.2803722000000001</v>
       </c>
       <c r="N16">
-        <v>3.37831928</v>
+        <v>3.3596278</v>
       </c>
       <c r="O16">
-        <v>0.675663856</v>
+        <v>0.67192556</v>
       </c>
       <c r="P16">
-        <v>2.702655424</v>
+        <v>2.68770224</v>
       </c>
       <c r="Q16">
-        <v>4.792655424</v>
+        <v>4.77770224</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1594305558395982</v>
+        <v>0.1605308275010806</v>
       </c>
       <c r="T16">
-        <v>1.244301160872877</v>
+        <v>1.256349586540976</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.91008095667117</v>
+        <v>12.98274222622642</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1424872033759185</v>
+        <v>0.1424225287297826</v>
       </c>
       <c r="C17">
-        <v>33.71587571763374</v>
+        <v>33.36912873695206</v>
       </c>
       <c r="D17">
-        <v>37.12987571763373</v>
+        <v>37.15472873695206</v>
       </c>
       <c r="E17">
-        <v>-2.986</v>
+        <v>-2.6144</v>
       </c>
       <c r="F17">
-        <v>5.574000000000001</v>
+        <v>5.945600000000001</v>
       </c>
       <c r="G17">
         <v>2.16</v>
@@ -2675,45 +2675,45 @@
         <v>3.64</v>
       </c>
       <c r="M17">
-        <v>0.2803722</v>
+        <v>0.30798208</v>
       </c>
       <c r="N17">
-        <v>3.3596278</v>
+        <v>3.33201792</v>
       </c>
       <c r="O17">
-        <v>0.67192556</v>
+        <v>0.6664035840000001</v>
       </c>
       <c r="P17">
-        <v>2.68770224</v>
+        <v>2.665614336</v>
       </c>
       <c r="Q17">
-        <v>4.77770224</v>
+        <v>4.755614336000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1605308275010806</v>
+        <v>0.161657296106884</v>
       </c>
       <c r="T17">
-        <v>1.256349586540976</v>
+        <v>1.268684879486886</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>12.98274222622642</v>
+        <v>11.81886946149594</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1424225287297826</v>
+        <v>0.1421778540836467</v>
       </c>
       <c r="C18">
-        <v>33.36912873695206</v>
+        <v>33.09185351926253</v>
       </c>
       <c r="D18">
-        <v>37.15472873695206</v>
+        <v>37.24905351926252</v>
       </c>
       <c r="E18">
-        <v>-2.6144</v>
+        <v>-2.242799999999999</v>
       </c>
       <c r="F18">
-        <v>5.945600000000001</v>
+        <v>6.317200000000001</v>
       </c>
       <c r="G18">
         <v>2.16</v>
@@ -2757,28 +2757,28 @@
         <v>3.64</v>
       </c>
       <c r="M18">
-        <v>0.30798208</v>
+        <v>0.3272309600000001</v>
       </c>
       <c r="N18">
-        <v>3.33201792</v>
+        <v>3.31276904</v>
       </c>
       <c r="O18">
-        <v>0.6664035840000001</v>
+        <v>0.6625538080000001</v>
       </c>
       <c r="P18">
-        <v>2.665614336</v>
+        <v>2.650215232</v>
       </c>
       <c r="Q18">
-        <v>4.755614336000001</v>
+        <v>4.740215232000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.161657296106884</v>
+        <v>0.1628109085345141</v>
       </c>
       <c r="T18">
-        <v>1.268684879486886</v>
+        <v>1.281317408407397</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.81886946149594</v>
+        <v>11.12364184611383</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1421778540836467</v>
+        <v>0.1419331794375108</v>
       </c>
       <c r="C19">
-        <v>33.09185351926253</v>
+        <v>32.81505844553301</v>
       </c>
       <c r="D19">
-        <v>37.24905351926252</v>
+        <v>37.34385844553302</v>
       </c>
       <c r="E19">
-        <v>-2.242799999999999</v>
+        <v>-1.871199999999999</v>
       </c>
       <c r="F19">
-        <v>6.317200000000001</v>
+        <v>6.688800000000001</v>
       </c>
       <c r="G19">
         <v>2.16</v>
@@ -2839,28 +2839,28 @@
         <v>3.64</v>
       </c>
       <c r="M19">
-        <v>0.3272309600000001</v>
+        <v>0.34647984</v>
       </c>
       <c r="N19">
-        <v>3.31276904</v>
+        <v>3.29352016</v>
       </c>
       <c r="O19">
-        <v>0.6625538080000001</v>
+        <v>0.6587040320000001</v>
       </c>
       <c r="P19">
-        <v>2.650215232</v>
+        <v>2.634816128</v>
       </c>
       <c r="Q19">
-        <v>4.740215232000001</v>
+        <v>4.724816128000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1628109085345141</v>
+        <v>0.1639926578506229</v>
       </c>
       <c r="T19">
-        <v>1.281317408407397</v>
+        <v>1.294258047789383</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.12364184611383</v>
+        <v>10.50566174355195</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1419331794375108</v>
+        <v>0.1416885047913749</v>
       </c>
       <c r="C20">
-        <v>32.81505844553303</v>
+        <v>32.53874719125275</v>
       </c>
       <c r="D20">
-        <v>37.34385844553303</v>
+        <v>37.43914719125275</v>
       </c>
       <c r="E20">
-        <v>-1.8712</v>
+        <v>-1.4996</v>
       </c>
       <c r="F20">
-        <v>6.688800000000001</v>
+        <v>7.0604</v>
       </c>
       <c r="G20">
         <v>2.16</v>
@@ -2921,28 +2921,28 @@
         <v>3.64</v>
       </c>
       <c r="M20">
-        <v>0.34647984</v>
+        <v>0.36572872</v>
       </c>
       <c r="N20">
-        <v>3.29352016</v>
+        <v>3.27427128</v>
       </c>
       <c r="O20">
-        <v>0.6587040320000001</v>
+        <v>0.6548542560000001</v>
       </c>
       <c r="P20">
-        <v>2.634816128</v>
+        <v>2.619417024</v>
       </c>
       <c r="Q20">
-        <v>4.724816128000001</v>
+        <v>4.709417024</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1639926578506229</v>
+        <v>0.1652035861621912</v>
       </c>
       <c r="T20">
-        <v>1.294258047789383</v>
+        <v>1.307518209131419</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.50566174355195</v>
+        <v>9.952732178101845</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1416885047913749</v>
+        <v>0.1417158301452389</v>
       </c>
       <c r="C21">
-        <v>32.53874719125275</v>
+        <v>32.15648119436963</v>
       </c>
       <c r="D21">
-        <v>37.43914719125275</v>
+        <v>37.42848119436964</v>
       </c>
       <c r="E21">
-        <v>-1.4996</v>
+        <v>-1.127999999999999</v>
       </c>
       <c r="F21">
-        <v>7.0604</v>
+        <v>7.432000000000001</v>
       </c>
       <c r="G21">
         <v>2.16</v>
@@ -3003,45 +3003,45 @@
         <v>3.64</v>
       </c>
       <c r="M21">
-        <v>0.36572872</v>
+        <v>0.3976120000000001</v>
       </c>
       <c r="N21">
-        <v>3.27427128</v>
+        <v>3.242388</v>
       </c>
       <c r="O21">
-        <v>0.6548542560000001</v>
+        <v>0.6484776000000001</v>
       </c>
       <c r="P21">
-        <v>2.619417024</v>
+        <v>2.5939104</v>
       </c>
       <c r="Q21">
-        <v>4.709417024</v>
+        <v>4.6839104</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1652035861621912</v>
+        <v>0.1664447876815487</v>
       </c>
       <c r="T21">
-        <v>1.307518209131419</v>
+        <v>1.321109874507005</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>9.952732178101845</v>
+        <v>9.154653280082089</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1417158301452389</v>
+        <v>0.141484755499103</v>
       </c>
       <c r="C22">
-        <v>32.15648119436963</v>
+        <v>31.87526939677744</v>
       </c>
       <c r="D22">
-        <v>37.42848119436964</v>
+        <v>37.51886939677745</v>
       </c>
       <c r="E22">
-        <v>-1.127999999999999</v>
+        <v>-0.7563999999999993</v>
       </c>
       <c r="F22">
-        <v>7.432000000000001</v>
+        <v>7.803600000000001</v>
       </c>
       <c r="G22">
         <v>2.16</v>
@@ -3085,28 +3085,28 @@
         <v>3.64</v>
       </c>
       <c r="M22">
-        <v>0.3976120000000001</v>
+        <v>0.4174926</v>
       </c>
       <c r="N22">
-        <v>3.242388</v>
+        <v>3.2225074</v>
       </c>
       <c r="O22">
-        <v>0.6484776000000001</v>
+        <v>0.6445014800000001</v>
       </c>
       <c r="P22">
-        <v>2.5939104</v>
+        <v>2.57800592</v>
       </c>
       <c r="Q22">
-        <v>4.6839104</v>
+        <v>4.668005920000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1664447876815487</v>
+        <v>0.1677174120241811</v>
       </c>
       <c r="T22">
-        <v>1.321109874507005</v>
+        <v>1.33504563267691</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.154653280082089</v>
+        <v>8.718717409601989</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.141484755499103</v>
+        <v>0.1412536808529671</v>
       </c>
       <c r="C23">
-        <v>31.87526939677744</v>
+        <v>31.59449522341723</v>
       </c>
       <c r="D23">
-        <v>37.51886939677745</v>
+        <v>37.60969522341723</v>
       </c>
       <c r="E23">
-        <v>-0.7564000000000002</v>
+        <v>-0.3848000000000003</v>
       </c>
       <c r="F23">
-        <v>7.8036</v>
+        <v>8.1752</v>
       </c>
       <c r="G23">
         <v>2.16</v>
@@ -3167,28 +3167,28 @@
         <v>3.64</v>
       </c>
       <c r="M23">
-        <v>0.4174926</v>
+        <v>0.4373732</v>
       </c>
       <c r="N23">
-        <v>3.2225074</v>
+        <v>3.2026268</v>
       </c>
       <c r="O23">
-        <v>0.6445014800000001</v>
+        <v>0.64052536</v>
       </c>
       <c r="P23">
-        <v>2.57800592</v>
+        <v>2.56210144</v>
       </c>
       <c r="Q23">
-        <v>4.668005920000001</v>
+        <v>4.652101440000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1677174120241811</v>
+        <v>0.1690226677602142</v>
       </c>
       <c r="T23">
-        <v>1.33504563267691</v>
+        <v>1.349338717979377</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.718717409601989</v>
+        <v>8.3224120728019</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1412536808529671</v>
+        <v>0.1410226062068312</v>
       </c>
       <c r="C24">
-        <v>31.59449522341723</v>
+        <v>31.31416186020884</v>
       </c>
       <c r="D24">
-        <v>37.60969522341723</v>
+        <v>37.70096186020884</v>
       </c>
       <c r="E24">
-        <v>-0.3848000000000003</v>
+        <v>-0.01319999999999943</v>
       </c>
       <c r="F24">
-        <v>8.1752</v>
+        <v>8.546800000000001</v>
       </c>
       <c r="G24">
         <v>2.16</v>
@@ -3249,28 +3249,28 @@
         <v>3.64</v>
       </c>
       <c r="M24">
-        <v>0.4373732</v>
+        <v>0.4572538</v>
       </c>
       <c r="N24">
-        <v>3.2026268</v>
+        <v>3.1827462</v>
       </c>
       <c r="O24">
-        <v>0.64052536</v>
+        <v>0.63654924</v>
       </c>
       <c r="P24">
-        <v>2.56210144</v>
+        <v>2.54619696</v>
       </c>
       <c r="Q24">
-        <v>4.652101440000001</v>
+        <v>4.63619696</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1690226677602142</v>
+        <v>0.1703618262426379</v>
       </c>
       <c r="T24">
-        <v>1.349338717979377</v>
+        <v>1.364003052250739</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.3224120728019</v>
+        <v>7.960568069636599</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1410226062068312</v>
+        <v>0.1407915315606953</v>
       </c>
       <c r="C25">
-        <v>31.31416186020884</v>
+        <v>31.03427252407221</v>
       </c>
       <c r="D25">
-        <v>37.70096186020884</v>
+        <v>37.79267252407222</v>
       </c>
       <c r="E25">
-        <v>-0.01319999999999943</v>
+        <v>0.3584000000000014</v>
       </c>
       <c r="F25">
-        <v>8.546800000000001</v>
+        <v>8.918400000000002</v>
       </c>
       <c r="G25">
         <v>2.16</v>
@@ -3331,28 +3331,28 @@
         <v>3.64</v>
       </c>
       <c r="M25">
-        <v>0.4572538</v>
+        <v>0.4771344000000001</v>
       </c>
       <c r="N25">
-        <v>3.1827462</v>
+        <v>3.1628656</v>
       </c>
       <c r="O25">
-        <v>0.63654924</v>
+        <v>0.63257312</v>
       </c>
       <c r="P25">
-        <v>2.54619696</v>
+        <v>2.53029248</v>
       </c>
       <c r="Q25">
-        <v>4.63619696</v>
+        <v>4.62029248</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1703618262426379</v>
+        <v>0.171736225737757</v>
       </c>
       <c r="T25">
-        <v>1.364003052250739</v>
+        <v>1.379053290055558</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.960568069636599</v>
+        <v>7.62887773340174</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1407915315606953</v>
+        <v>0.1407204569145594</v>
       </c>
       <c r="C26">
-        <v>31.03427252407223</v>
+        <v>30.69097096377103</v>
       </c>
       <c r="D26">
-        <v>37.79267252407223</v>
+        <v>37.82097096377103</v>
       </c>
       <c r="E26">
-        <v>0.3583999999999996</v>
+        <v>0.7300000000000004</v>
       </c>
       <c r="F26">
-        <v>8.9184</v>
+        <v>9.290000000000001</v>
       </c>
       <c r="G26">
         <v>2.16</v>
@@ -3413,45 +3413,45 @@
         <v>3.64</v>
       </c>
       <c r="M26">
-        <v>0.4771344</v>
+        <v>0.5044470000000001</v>
       </c>
       <c r="N26">
-        <v>3.1628656</v>
+        <v>3.135553</v>
       </c>
       <c r="O26">
-        <v>0.63257312</v>
+        <v>0.6271106</v>
       </c>
       <c r="P26">
-        <v>2.53029248</v>
+        <v>2.5084424</v>
       </c>
       <c r="Q26">
-        <v>4.62029248</v>
+        <v>4.5984424</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.171736225737757</v>
+        <v>0.1731472758860791</v>
       </c>
       <c r="T26">
-        <v>1.379053290055558</v>
+        <v>1.394504867535172</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.628877733401741</v>
+        <v>7.215822474908165</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1407204569145594</v>
+        <v>0.1404957822684235</v>
       </c>
       <c r="C27">
-        <v>30.69097096377103</v>
+        <v>30.40910477307327</v>
       </c>
       <c r="D27">
-        <v>37.82097096377103</v>
+        <v>37.91070477307328</v>
       </c>
       <c r="E27">
-        <v>0.7300000000000004</v>
+        <v>1.101600000000001</v>
       </c>
       <c r="F27">
-        <v>9.290000000000001</v>
+        <v>9.661600000000002</v>
       </c>
       <c r="G27">
         <v>2.16</v>
@@ -3495,28 +3495,28 @@
         <v>3.64</v>
       </c>
       <c r="M27">
-        <v>0.5044470000000001</v>
+        <v>0.5246248800000001</v>
       </c>
       <c r="N27">
-        <v>3.135553</v>
+        <v>3.11537512</v>
       </c>
       <c r="O27">
-        <v>0.6271106</v>
+        <v>0.623075024</v>
       </c>
       <c r="P27">
-        <v>2.5084424</v>
+        <v>2.492300096</v>
       </c>
       <c r="Q27">
-        <v>4.5984424</v>
+        <v>4.582300096000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1731472758860791</v>
+        <v>0.1745964625248966</v>
       </c>
       <c r="T27">
-        <v>1.394504867535172</v>
+        <v>1.410374055216938</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.215822474908165</v>
+        <v>6.938290841257852</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1404957822684235</v>
+        <v>0.1402711076222875</v>
       </c>
       <c r="C28">
-        <v>30.40910477307327</v>
+        <v>30.12766539883527</v>
       </c>
       <c r="D28">
-        <v>37.91070477307328</v>
+        <v>38.00086539883527</v>
       </c>
       <c r="E28">
-        <v>1.101600000000001</v>
+        <v>1.4732</v>
       </c>
       <c r="F28">
-        <v>9.661600000000002</v>
+        <v>10.0332</v>
       </c>
       <c r="G28">
         <v>2.16</v>
@@ -3577,28 +3577,28 @@
         <v>3.64</v>
       </c>
       <c r="M28">
-        <v>0.5246248800000001</v>
+        <v>0.5448027600000001</v>
       </c>
       <c r="N28">
-        <v>3.11537512</v>
+        <v>3.09519724</v>
       </c>
       <c r="O28">
-        <v>0.623075024</v>
+        <v>0.6190394480000001</v>
       </c>
       <c r="P28">
-        <v>2.492300096</v>
+        <v>2.476157792</v>
       </c>
       <c r="Q28">
-        <v>4.582300096000001</v>
+        <v>4.566157792</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1745964625248966</v>
+        <v>0.1760853529072432</v>
       </c>
       <c r="T28">
-        <v>1.410374055216938</v>
+        <v>1.426678015163958</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.938290841257852</v>
+        <v>6.681317106396451</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1402711076222875</v>
+        <v>0.1400464329761516</v>
       </c>
       <c r="C29">
-        <v>30.12766539883527</v>
+        <v>29.84665589352807</v>
       </c>
       <c r="D29">
-        <v>38.00086539883527</v>
+        <v>38.09145589352807</v>
       </c>
       <c r="E29">
-        <v>1.4732</v>
+        <v>1.844800000000001</v>
       </c>
       <c r="F29">
-        <v>10.0332</v>
+        <v>10.4048</v>
       </c>
       <c r="G29">
         <v>2.16</v>
@@ -3659,28 +3659,28 @@
         <v>3.64</v>
       </c>
       <c r="M29">
-        <v>0.5448027600000001</v>
+        <v>0.5649806400000001</v>
       </c>
       <c r="N29">
-        <v>3.09519724</v>
+        <v>3.07501936</v>
       </c>
       <c r="O29">
-        <v>0.6190394480000001</v>
+        <v>0.615003872</v>
       </c>
       <c r="P29">
-        <v>2.476157792</v>
+        <v>2.460015488</v>
       </c>
       <c r="Q29">
-        <v>4.566157792</v>
+        <v>4.550015488</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1760853529072432</v>
+        <v>0.1776156013557662</v>
       </c>
       <c r="T29">
-        <v>1.426678015163958</v>
+        <v>1.443434862887284</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.681317106396451</v>
+        <v>6.442698638310861</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1400464329761516</v>
+        <v>0.1398217583300157</v>
       </c>
       <c r="C30">
-        <v>29.84665589352807</v>
+        <v>29.56607933879953</v>
       </c>
       <c r="D30">
-        <v>38.09145589352807</v>
+        <v>38.18247933879954</v>
       </c>
       <c r="E30">
-        <v>1.844800000000001</v>
+        <v>2.216400000000002</v>
       </c>
       <c r="F30">
-        <v>10.4048</v>
+        <v>10.7764</v>
       </c>
       <c r="G30">
         <v>2.16</v>
@@ -3741,28 +3741,28 @@
         <v>3.64</v>
       </c>
       <c r="M30">
-        <v>0.5649806400000001</v>
+        <v>0.5851585200000001</v>
       </c>
       <c r="N30">
-        <v>3.07501936</v>
+        <v>3.05484148</v>
       </c>
       <c r="O30">
-        <v>0.615003872</v>
+        <v>0.610968296</v>
       </c>
       <c r="P30">
-        <v>2.460015488</v>
+        <v>2.443873184</v>
       </c>
       <c r="Q30">
-        <v>4.550015488</v>
+        <v>4.533873184000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1776156013557662</v>
+        <v>0.1791889553943883</v>
       </c>
       <c r="T30">
-        <v>1.443434862887284</v>
+        <v>1.46066373449014</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.442698638310861</v>
+        <v>6.220536616300143</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1398217583300157</v>
+        <v>0.1398370836838798</v>
       </c>
       <c r="C31">
-        <v>29.56607933879955</v>
+        <v>29.18825668722048</v>
       </c>
       <c r="D31">
-        <v>38.18247933879955</v>
+        <v>38.17625668722048</v>
       </c>
       <c r="E31">
-        <v>2.2164</v>
+        <v>2.588000000000001</v>
       </c>
       <c r="F31">
-        <v>10.7764</v>
+        <v>11.148</v>
       </c>
       <c r="G31">
         <v>2.16</v>
@@ -3823,45 +3823,45 @@
         <v>3.64</v>
       </c>
       <c r="M31">
-        <v>0.58515852</v>
+        <v>0.6164844000000002</v>
       </c>
       <c r="N31">
-        <v>3.05484148</v>
+        <v>3.0235156</v>
       </c>
       <c r="O31">
-        <v>0.6109682960000001</v>
+        <v>0.60470312</v>
       </c>
       <c r="P31">
-        <v>2.443873184</v>
+        <v>2.41881248</v>
       </c>
       <c r="Q31">
-        <v>4.533873184000001</v>
+        <v>4.50881248</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1791889553943883</v>
+        <v>0.1808072624055426</v>
       </c>
       <c r="T31">
-        <v>1.46066373449014</v>
+        <v>1.478384859567363</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.220536616300144</v>
+        <v>5.904447865996284</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1398370836838798</v>
+        <v>0.1396204090377439</v>
       </c>
       <c r="C32">
-        <v>29.18825668722048</v>
+        <v>28.90482329183602</v>
       </c>
       <c r="D32">
-        <v>38.17625668722048</v>
+        <v>38.26442329183602</v>
       </c>
       <c r="E32">
-        <v>2.588000000000001</v>
+        <v>2.9596</v>
       </c>
       <c r="F32">
-        <v>11.148</v>
+        <v>11.5196</v>
       </c>
       <c r="G32">
         <v>2.16</v>
@@ -3905,28 +3905,28 @@
         <v>3.64</v>
       </c>
       <c r="M32">
-        <v>0.6164844000000002</v>
+        <v>0.6370338800000001</v>
       </c>
       <c r="N32">
-        <v>3.0235156</v>
+        <v>3.00296612</v>
       </c>
       <c r="O32">
-        <v>0.60470312</v>
+        <v>0.600593224</v>
       </c>
       <c r="P32">
-        <v>2.41881248</v>
+        <v>2.402372896</v>
       </c>
       <c r="Q32">
-        <v>4.50881248</v>
+        <v>4.492372896000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1808072624055426</v>
+        <v>0.1824724768662955</v>
       </c>
       <c r="T32">
-        <v>1.478384859567363</v>
+        <v>1.496619640443926</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.904447865996284</v>
+        <v>5.713981805802856</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1396204090377439</v>
+        <v>0.1394037343916079</v>
       </c>
       <c r="C33">
-        <v>28.90482329183602</v>
+        <v>28.62179807392395</v>
       </c>
       <c r="D33">
-        <v>38.26442329183602</v>
+        <v>38.35299807392396</v>
       </c>
       <c r="E33">
-        <v>2.9596</v>
+        <v>3.331200000000001</v>
       </c>
       <c r="F33">
-        <v>11.5196</v>
+        <v>11.8912</v>
       </c>
       <c r="G33">
         <v>2.16</v>
@@ -3987,28 +3987,28 @@
         <v>3.64</v>
       </c>
       <c r="M33">
-        <v>0.6370338800000001</v>
+        <v>0.6575833600000001</v>
       </c>
       <c r="N33">
-        <v>3.00296612</v>
+        <v>2.98241664</v>
       </c>
       <c r="O33">
-        <v>0.600593224</v>
+        <v>0.596483328</v>
       </c>
       <c r="P33">
-        <v>2.402372896</v>
+        <v>2.385933312</v>
       </c>
       <c r="Q33">
-        <v>4.492372896000001</v>
+        <v>4.475933312</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1824724768662955</v>
+        <v>0.1841866682229529</v>
       </c>
       <c r="T33">
-        <v>1.496619640443926</v>
+        <v>1.515390738405094</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.713981805802856</v>
+        <v>5.535419874371517</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1394037343916079</v>
+        <v>0.139187059745472</v>
       </c>
       <c r="C34">
-        <v>28.62179807392395</v>
+        <v>28.33918387461805</v>
       </c>
       <c r="D34">
-        <v>38.35299807392396</v>
+        <v>38.44198387461805</v>
       </c>
       <c r="E34">
-        <v>3.331200000000001</v>
+        <v>3.702800000000002</v>
       </c>
       <c r="F34">
-        <v>11.8912</v>
+        <v>12.2628</v>
       </c>
       <c r="G34">
         <v>2.16</v>
@@ -4069,28 +4069,28 @@
         <v>3.64</v>
       </c>
       <c r="M34">
-        <v>0.6575833600000001</v>
+        <v>0.6781328400000002</v>
       </c>
       <c r="N34">
-        <v>2.98241664</v>
+        <v>2.96186716</v>
       </c>
       <c r="O34">
-        <v>0.596483328</v>
+        <v>0.5923734319999999</v>
       </c>
       <c r="P34">
-        <v>2.385933312</v>
+        <v>2.369493728</v>
       </c>
       <c r="Q34">
-        <v>4.475933312</v>
+        <v>4.459493728</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1841866682229529</v>
+        <v>0.1859520294708538</v>
       </c>
       <c r="T34">
-        <v>1.515390738405094</v>
+        <v>1.534722167648685</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.535419874371517</v>
+        <v>5.367679878178439</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.139187059745472</v>
+        <v>0.1389703850993361</v>
       </c>
       <c r="C35">
-        <v>28.33918387461805</v>
+        <v>28.05698356148116</v>
       </c>
       <c r="D35">
-        <v>38.44198387461805</v>
+        <v>38.53138356148116</v>
       </c>
       <c r="E35">
-        <v>3.702800000000002</v>
+        <v>4.074400000000002</v>
       </c>
       <c r="F35">
-        <v>12.2628</v>
+        <v>12.6344</v>
       </c>
       <c r="G35">
         <v>2.16</v>
@@ -4151,28 +4151,28 @@
         <v>3.64</v>
       </c>
       <c r="M35">
-        <v>0.6781328400000002</v>
+        <v>0.6986823200000002</v>
       </c>
       <c r="N35">
-        <v>2.96186716</v>
+        <v>2.94131768</v>
       </c>
       <c r="O35">
-        <v>0.5923734319999999</v>
+        <v>0.588263536</v>
       </c>
       <c r="P35">
-        <v>2.369493728</v>
+        <v>2.353054144</v>
       </c>
       <c r="Q35">
-        <v>4.459493728</v>
+        <v>4.443054144</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1859520294708538</v>
+        <v>0.1877708865141457</v>
       </c>
       <c r="T35">
-        <v>1.534722167648685</v>
+        <v>1.554639397778446</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.367679878178439</v>
+        <v>5.209806940584956</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1389703850993361</v>
+        <v>0.1387537104532002</v>
       </c>
       <c r="C36">
-        <v>28.05698356148116</v>
+        <v>27.77520002881319</v>
       </c>
       <c r="D36">
-        <v>38.53138356148116</v>
+        <v>38.62120002881318</v>
       </c>
       <c r="E36">
-        <v>4.074400000000002</v>
+        <v>4.446000000000002</v>
       </c>
       <c r="F36">
-        <v>12.6344</v>
+        <v>13.006</v>
       </c>
       <c r="G36">
         <v>2.16</v>
@@ -4233,28 +4233,28 @@
         <v>3.64</v>
       </c>
       <c r="M36">
-        <v>0.6986823200000002</v>
+        <v>0.7192318000000001</v>
       </c>
       <c r="N36">
-        <v>2.94131768</v>
+        <v>2.9207682</v>
       </c>
       <c r="O36">
-        <v>0.588263536</v>
+        <v>0.58415364</v>
       </c>
       <c r="P36">
-        <v>2.353054144</v>
+        <v>2.33661456</v>
       </c>
       <c r="Q36">
-        <v>4.443054144</v>
+        <v>4.426614560000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1877708865141457</v>
+        <v>0.1896457083895388</v>
       </c>
       <c r="T36">
-        <v>1.554639397778446</v>
+        <v>1.575169465758352</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.209806940584956</v>
+        <v>5.060955313711101</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1387537104532002</v>
+        <v>0.1385370358070643</v>
       </c>
       <c r="C37">
-        <v>27.77520002881319</v>
+        <v>27.49383619796353</v>
       </c>
       <c r="D37">
-        <v>38.62120002881318</v>
+        <v>38.71143619796353</v>
       </c>
       <c r="E37">
-        <v>4.446000000000002</v>
+        <v>4.817600000000002</v>
       </c>
       <c r="F37">
-        <v>13.006</v>
+        <v>13.3776</v>
       </c>
       <c r="G37">
         <v>2.16</v>
@@ -4315,28 +4315,28 @@
         <v>3.64</v>
       </c>
       <c r="M37">
-        <v>0.7192318000000001</v>
+        <v>0.7397812800000002</v>
       </c>
       <c r="N37">
-        <v>2.9207682</v>
+        <v>2.90021872</v>
       </c>
       <c r="O37">
-        <v>0.58415364</v>
+        <v>0.580043744</v>
       </c>
       <c r="P37">
-        <v>2.33661456</v>
+        <v>2.320174976</v>
       </c>
       <c r="Q37">
-        <v>4.426614560000001</v>
+        <v>4.410174976</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1896457083895388</v>
+        <v>0.191579118448538</v>
       </c>
       <c r="T37">
-        <v>1.575169465758352</v>
+        <v>1.596341098362632</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.060955313711101</v>
+        <v>4.920373221663569</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1385370358070643</v>
+        <v>0.1383203611609284</v>
       </c>
       <c r="C38">
-        <v>27.49383619796353</v>
+        <v>27.21289501764772</v>
       </c>
       <c r="D38">
-        <v>38.71143619796353</v>
+        <v>38.80209501764773</v>
       </c>
       <c r="E38">
-        <v>4.817600000000001</v>
+        <v>5.189200000000001</v>
       </c>
       <c r="F38">
-        <v>13.3776</v>
+        <v>13.7492</v>
       </c>
       <c r="G38">
         <v>2.16</v>
@@ -4397,28 +4397,28 @@
         <v>3.64</v>
       </c>
       <c r="M38">
-        <v>0.7397812800000001</v>
+        <v>0.7603307600000001</v>
       </c>
       <c r="N38">
-        <v>2.90021872</v>
+        <v>2.87966924</v>
       </c>
       <c r="O38">
-        <v>0.580043744</v>
+        <v>0.575933848</v>
       </c>
       <c r="P38">
-        <v>2.320174976</v>
+        <v>2.303735392</v>
       </c>
       <c r="Q38">
-        <v>4.410174976</v>
+        <v>4.393735392</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.191579118448538</v>
+        <v>0.1935739066046483</v>
       </c>
       <c r="T38">
-        <v>1.596341098362631</v>
+        <v>1.618184846287681</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.92037322166357</v>
+        <v>4.787390161618609</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1383203611609284</v>
+        <v>0.1381036865147925</v>
       </c>
       <c r="C39">
-        <v>27.21289501764772</v>
+        <v>26.93237946426878</v>
       </c>
       <c r="D39">
-        <v>38.80209501764773</v>
+        <v>38.89317946426878</v>
       </c>
       <c r="E39">
-        <v>5.189200000000001</v>
+        <v>5.5608</v>
       </c>
       <c r="F39">
-        <v>13.7492</v>
+        <v>14.1208</v>
       </c>
       <c r="G39">
         <v>2.16</v>
@@ -4479,28 +4479,28 @@
         <v>3.64</v>
       </c>
       <c r="M39">
-        <v>0.7603307600000001</v>
+        <v>0.7808802400000001</v>
       </c>
       <c r="N39">
-        <v>2.87966924</v>
+        <v>2.85911976</v>
       </c>
       <c r="O39">
-        <v>0.575933848</v>
+        <v>0.571823952</v>
       </c>
       <c r="P39">
-        <v>2.303735392</v>
+        <v>2.287295808</v>
       </c>
       <c r="Q39">
-        <v>4.393735392</v>
+        <v>4.377295808</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1935739066046483</v>
+        <v>0.1956330427657943</v>
       </c>
       <c r="T39">
-        <v>1.618184846287681</v>
+        <v>1.640733231242571</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.787390161618609</v>
+        <v>4.661406209997066</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1381036865147925</v>
+        <v>0.1378870118686566</v>
       </c>
       <c r="C40">
-        <v>26.93237946426878</v>
+        <v>26.65229254224268</v>
       </c>
       <c r="D40">
-        <v>38.89317946426878</v>
+        <v>38.98469254224268</v>
       </c>
       <c r="E40">
-        <v>5.5608</v>
+        <v>5.932400000000001</v>
       </c>
       <c r="F40">
-        <v>14.1208</v>
+        <v>14.4924</v>
       </c>
       <c r="G40">
         <v>2.16</v>
@@ -4561,28 +4561,28 @@
         <v>3.64</v>
       </c>
       <c r="M40">
-        <v>0.7808802400000001</v>
+        <v>0.8014297200000001</v>
       </c>
       <c r="N40">
-        <v>2.85911976</v>
+        <v>2.83857028</v>
       </c>
       <c r="O40">
-        <v>0.571823952</v>
+        <v>0.567714056</v>
       </c>
       <c r="P40">
-        <v>2.287295808</v>
+        <v>2.270856224</v>
       </c>
       <c r="Q40">
-        <v>4.377295808</v>
+        <v>4.360856224000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1956330427657943</v>
+        <v>0.1977596915879616</v>
       </c>
       <c r="T40">
-        <v>1.640733231242571</v>
+        <v>1.664020907507457</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.661406209997066</v>
+        <v>4.541882973843295</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1378870118686566</v>
+        <v>0.1384703372225207</v>
       </c>
       <c r="C41">
-        <v>26.65229254224268</v>
+        <v>26.03529838210402</v>
       </c>
       <c r="D41">
-        <v>38.98469254224268</v>
+        <v>38.73929838210402</v>
       </c>
       <c r="E41">
-        <v>5.932400000000001</v>
+        <v>6.304000000000002</v>
       </c>
       <c r="F41">
-        <v>14.4924</v>
+        <v>14.864</v>
       </c>
       <c r="G41">
         <v>2.16</v>
@@ -4643,45 +4643,45 @@
         <v>3.64</v>
       </c>
       <c r="M41">
-        <v>0.8014297200000001</v>
+        <v>0.8591392000000002</v>
       </c>
       <c r="N41">
-        <v>2.83857028</v>
+        <v>2.7808608</v>
       </c>
       <c r="O41">
-        <v>0.567714056</v>
+        <v>0.55617216</v>
       </c>
       <c r="P41">
-        <v>2.270856224</v>
+        <v>2.22468864</v>
       </c>
       <c r="Q41">
-        <v>4.360856224000001</v>
+        <v>4.31468864</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1977596915879616</v>
+        <v>0.1999572287042011</v>
       </c>
       <c r="T41">
-        <v>1.664020907507457</v>
+        <v>1.68808483964784</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.541882973843295</v>
+        <v>4.236798879622766</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1384703372225207</v>
+        <v>0.1382736625763847</v>
       </c>
       <c r="C42">
-        <v>26.03529838210402</v>
+        <v>25.74608981755257</v>
       </c>
       <c r="D42">
-        <v>38.73929838210402</v>
+        <v>38.82168981755258</v>
       </c>
       <c r="E42">
-        <v>6.304000000000002</v>
+        <v>6.675600000000003</v>
       </c>
       <c r="F42">
-        <v>14.864</v>
+        <v>15.2356</v>
       </c>
       <c r="G42">
         <v>2.16</v>
@@ -4725,28 +4725,28 @@
         <v>3.64</v>
       </c>
       <c r="M42">
-        <v>0.8591392000000002</v>
+        <v>0.8806176800000003</v>
       </c>
       <c r="N42">
-        <v>2.7808608</v>
+        <v>2.75938232</v>
       </c>
       <c r="O42">
-        <v>0.55617216</v>
+        <v>0.551876464</v>
       </c>
       <c r="P42">
-        <v>2.22468864</v>
+        <v>2.207505856</v>
       </c>
       <c r="Q42">
-        <v>4.31468864</v>
+        <v>4.297505856000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1999572287042011</v>
+        <v>0.2022292586040419</v>
       </c>
       <c r="T42">
-        <v>1.68808483964784</v>
+        <v>1.712964498301456</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.236798879622766</v>
+        <v>4.133462321583186</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1382736625763847</v>
+        <v>0.1380769879302488</v>
       </c>
       <c r="C43">
-        <v>25.74608981755257</v>
+        <v>25.45723246313002</v>
       </c>
       <c r="D43">
-        <v>38.82168981755258</v>
+        <v>38.90443246313002</v>
       </c>
       <c r="E43">
-        <v>6.675600000000003</v>
+        <v>7.047200000000002</v>
       </c>
       <c r="F43">
-        <v>15.2356</v>
+        <v>15.6072</v>
       </c>
       <c r="G43">
         <v>2.16</v>
@@ -4807,28 +4807,28 @@
         <v>3.64</v>
       </c>
       <c r="M43">
-        <v>0.8806176800000003</v>
+        <v>0.9020961600000003</v>
       </c>
       <c r="N43">
-        <v>2.75938232</v>
+        <v>2.73790384</v>
       </c>
       <c r="O43">
-        <v>0.551876464</v>
+        <v>0.547580768</v>
       </c>
       <c r="P43">
-        <v>2.207505856</v>
+        <v>2.190323072</v>
       </c>
       <c r="Q43">
-        <v>4.297505856000001</v>
+        <v>4.280323072</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2022292586040419</v>
+        <v>0.204579634362498</v>
       </c>
       <c r="T43">
-        <v>1.712964498301456</v>
+        <v>1.73870207621899</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.133462321583186</v>
+        <v>4.035046552021681</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1380769879302488</v>
+        <v>0.1390843132841129</v>
       </c>
       <c r="C44">
-        <v>25.45723246313002</v>
+        <v>24.66552516086103</v>
       </c>
       <c r="D44">
-        <v>38.90443246313001</v>
+        <v>38.48432516086103</v>
       </c>
       <c r="E44">
-        <v>7.0472</v>
+        <v>7.418800000000001</v>
       </c>
       <c r="F44">
-        <v>15.6072</v>
+        <v>15.9788</v>
       </c>
       <c r="G44">
         <v>2.16</v>
@@ -4889,45 +4889,45 @@
         <v>3.64</v>
       </c>
       <c r="M44">
-        <v>0.9020961600000001</v>
+        <v>0.9795004400000001</v>
       </c>
       <c r="N44">
-        <v>2.73790384</v>
+        <v>2.66049956</v>
       </c>
       <c r="O44">
-        <v>0.547580768</v>
+        <v>0.532099912</v>
       </c>
       <c r="P44">
-        <v>2.190323072</v>
+        <v>2.128399648</v>
       </c>
       <c r="Q44">
-        <v>4.280323072</v>
+        <v>4.218399648</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.204579634362498</v>
+        <v>0.2070124794458121</v>
       </c>
       <c r="T44">
-        <v>1.73870207621899</v>
+        <v>1.765342727045911</v>
       </c>
       <c r="U44">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.035046552021682</v>
+        <v>3.716180056029377</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1390843132841129</v>
+        <v>0.138915638637977</v>
       </c>
       <c r="C45">
-        <v>24.66552516086103</v>
+        <v>24.36363772497203</v>
       </c>
       <c r="D45">
-        <v>38.48432516086103</v>
+        <v>38.55403772497203</v>
       </c>
       <c r="E45">
-        <v>7.418800000000001</v>
+        <v>7.7904</v>
       </c>
       <c r="F45">
-        <v>15.9788</v>
+        <v>16.3504</v>
       </c>
       <c r="G45">
         <v>2.16</v>
@@ -4971,28 +4971,28 @@
         <v>3.64</v>
       </c>
       <c r="M45">
-        <v>0.9795004400000001</v>
+        <v>1.00227952</v>
       </c>
       <c r="N45">
-        <v>2.66049956</v>
+        <v>2.63772048</v>
       </c>
       <c r="O45">
-        <v>0.532099912</v>
+        <v>0.5275440960000001</v>
       </c>
       <c r="P45">
-        <v>2.128399648</v>
+        <v>2.110176384</v>
       </c>
       <c r="Q45">
-        <v>4.218399648</v>
+        <v>4.200176384000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2070124794458121</v>
+        <v>0.2095322118535304</v>
       </c>
       <c r="T45">
-        <v>1.765342727045911</v>
+        <v>1.792934829688078</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.716180056029377</v>
+        <v>3.631721418392346</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.138915638637977</v>
+        <v>0.1387469639918411</v>
       </c>
       <c r="C46">
-        <v>24.36363772497203</v>
+        <v>24.06200330954929</v>
       </c>
       <c r="D46">
-        <v>38.55403772497203</v>
+        <v>38.62400330954929</v>
       </c>
       <c r="E46">
-        <v>7.7904</v>
+        <v>8.162000000000001</v>
       </c>
       <c r="F46">
-        <v>16.3504</v>
+        <v>16.722</v>
       </c>
       <c r="G46">
         <v>2.16</v>
@@ -5053,28 +5053,28 @@
         <v>3.64</v>
       </c>
       <c r="M46">
-        <v>1.00227952</v>
+        <v>1.0250586</v>
       </c>
       <c r="N46">
-        <v>2.63772048</v>
+        <v>2.6149414</v>
       </c>
       <c r="O46">
-        <v>0.5275440960000001</v>
+        <v>0.5229882800000001</v>
       </c>
       <c r="P46">
-        <v>2.110176384</v>
+        <v>2.09195312</v>
       </c>
       <c r="Q46">
-        <v>4.200176384000001</v>
+        <v>4.181953120000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2095322118535304</v>
+        <v>0.2121435708942565</v>
       </c>
       <c r="T46">
-        <v>1.792934829688078</v>
+        <v>1.821530281517235</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.631721418392346</v>
+        <v>3.551016497983627</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1387469639918411</v>
+        <v>0.1396086893457052</v>
       </c>
       <c r="C47">
-        <v>24.06200330954929</v>
+        <v>23.33560373659169</v>
       </c>
       <c r="D47">
-        <v>38.62400330954929</v>
+        <v>38.26920373659168</v>
       </c>
       <c r="E47">
-        <v>8.162000000000001</v>
+        <v>8.533600000000002</v>
       </c>
       <c r="F47">
-        <v>16.722</v>
+        <v>17.0936</v>
       </c>
       <c r="G47">
         <v>2.16</v>
@@ -5135,45 +5135,45 @@
         <v>3.64</v>
       </c>
       <c r="M47">
-        <v>1.0250586</v>
+        <v>1.09569976</v>
       </c>
       <c r="N47">
-        <v>2.6149414</v>
+        <v>2.54430024</v>
       </c>
       <c r="O47">
-        <v>0.5229882800000001</v>
+        <v>0.5088600480000001</v>
       </c>
       <c r="P47">
-        <v>2.09195312</v>
+        <v>2.035440192</v>
       </c>
       <c r="Q47">
-        <v>4.181953120000001</v>
+        <v>4.125440192000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2121435708942565</v>
+        <v>0.2148516469364911</v>
       </c>
       <c r="T47">
-        <v>1.821530281517235</v>
+        <v>1.851184824154878</v>
       </c>
       <c r="U47">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.551016497983627</v>
+        <v>3.322077938576896</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1396086893457052</v>
+        <v>0.1394624146995693</v>
       </c>
       <c r="C48">
-        <v>23.33560373659169</v>
+        <v>23.02376959093601</v>
       </c>
       <c r="D48">
-        <v>38.26920373659168</v>
+        <v>38.32896959093601</v>
       </c>
       <c r="E48">
-        <v>8.533600000000002</v>
+        <v>8.905200000000002</v>
       </c>
       <c r="F48">
-        <v>17.0936</v>
+        <v>17.4652</v>
       </c>
       <c r="G48">
         <v>2.16</v>
@@ -5217,28 +5217,28 @@
         <v>3.64</v>
       </c>
       <c r="M48">
-        <v>1.09569976</v>
+        <v>1.11951932</v>
       </c>
       <c r="N48">
-        <v>2.54430024</v>
+        <v>2.52048068</v>
       </c>
       <c r="O48">
-        <v>0.5088600480000001</v>
+        <v>0.504096136</v>
       </c>
       <c r="P48">
-        <v>2.035440192</v>
+        <v>2.016384544</v>
       </c>
       <c r="Q48">
-        <v>4.125440192000001</v>
+        <v>4.106384544000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2148516469364911</v>
+        <v>0.2176619145274892</v>
       </c>
       <c r="T48">
-        <v>1.851184824154878</v>
+        <v>1.881958406137338</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.322077938576896</v>
+        <v>3.251395429245473</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1394624146995693</v>
+        <v>0.1393161400534333</v>
       </c>
       <c r="C49">
-        <v>23.02376959093601</v>
+        <v>22.71212241256087</v>
       </c>
       <c r="D49">
-        <v>38.32896959093601</v>
+        <v>38.38892241256087</v>
       </c>
       <c r="E49">
-        <v>8.905200000000002</v>
+        <v>9.276800000000003</v>
       </c>
       <c r="F49">
-        <v>17.4652</v>
+        <v>17.8368</v>
       </c>
       <c r="G49">
         <v>2.16</v>
@@ -5299,28 +5299,28 @@
         <v>3.64</v>
       </c>
       <c r="M49">
-        <v>1.11951932</v>
+        <v>1.14333888</v>
       </c>
       <c r="N49">
-        <v>2.52048068</v>
+        <v>2.49666112</v>
       </c>
       <c r="O49">
-        <v>0.504096136</v>
+        <v>0.499332224</v>
       </c>
       <c r="P49">
-        <v>2.016384544</v>
+        <v>1.997328896</v>
       </c>
       <c r="Q49">
-        <v>4.106384544000001</v>
+        <v>4.087328896</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2176619145274892</v>
+        <v>0.2205802693335256</v>
       </c>
       <c r="T49">
-        <v>1.881958406137338</v>
+        <v>1.913915587426815</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.251395429245473</v>
+        <v>3.183658024469525</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1393161400534333</v>
+        <v>0.1391698654072974</v>
       </c>
       <c r="C50">
-        <v>22.71212241256087</v>
+        <v>22.40066308018357</v>
       </c>
       <c r="D50">
-        <v>38.38892241256087</v>
+        <v>38.44906308018358</v>
       </c>
       <c r="E50">
-        <v>9.2768</v>
+        <v>9.648400000000001</v>
       </c>
       <c r="F50">
-        <v>17.8368</v>
+        <v>18.2084</v>
       </c>
       <c r="G50">
         <v>2.16</v>
@@ -5381,28 +5381,28 @@
         <v>3.64</v>
       </c>
       <c r="M50">
-        <v>1.14333888</v>
+        <v>1.16715844</v>
       </c>
       <c r="N50">
-        <v>2.49666112</v>
+        <v>2.47284156</v>
       </c>
       <c r="O50">
-        <v>0.499332224</v>
+        <v>0.494568312</v>
       </c>
       <c r="P50">
-        <v>1.997328896</v>
+        <v>1.978273248</v>
       </c>
       <c r="Q50">
-        <v>4.087328896</v>
+        <v>4.068273248000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2205802693335256</v>
+        <v>0.2236130694260734</v>
       </c>
       <c r="T50">
-        <v>1.913915587426815</v>
+        <v>1.947125991511959</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.183658024469525</v>
+        <v>3.118685411725249</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1391698654072974</v>
+        <v>0.1390235907611615</v>
       </c>
       <c r="C51">
-        <v>22.40066308018357</v>
+        <v>22.08939247803653</v>
       </c>
       <c r="D51">
-        <v>38.44906308018358</v>
+        <v>38.50939247803652</v>
       </c>
       <c r="E51">
-        <v>9.648400000000001</v>
+        <v>10.02</v>
       </c>
       <c r="F51">
-        <v>18.2084</v>
+        <v>18.58</v>
       </c>
       <c r="G51">
         <v>2.16</v>
@@ -5463,28 +5463,28 @@
         <v>3.64</v>
       </c>
       <c r="M51">
-        <v>1.16715844</v>
+        <v>1.190978</v>
       </c>
       <c r="N51">
-        <v>2.47284156</v>
+        <v>2.449022</v>
       </c>
       <c r="O51">
-        <v>0.494568312</v>
+        <v>0.4898044000000001</v>
       </c>
       <c r="P51">
-        <v>1.978273248</v>
+        <v>1.9592176</v>
       </c>
       <c r="Q51">
-        <v>4.068273248000001</v>
+        <v>4.0492176</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2236130694260734</v>
+        <v>0.226767181522323</v>
       </c>
       <c r="T51">
-        <v>1.947125991511959</v>
+        <v>1.981664811760508</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.118685411725249</v>
+        <v>3.056311703490745</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1390235907611615</v>
+        <v>0.1420597161150256</v>
       </c>
       <c r="C52">
-        <v>22.08939247803653</v>
+        <v>20.5031686708693</v>
       </c>
       <c r="D52">
-        <v>38.50939247803652</v>
+        <v>37.2947686708693</v>
       </c>
       <c r="E52">
-        <v>10.02</v>
+        <v>10.3916</v>
       </c>
       <c r="F52">
-        <v>18.58</v>
+        <v>18.9516</v>
       </c>
       <c r="G52">
         <v>2.16</v>
@@ -5545,45 +5545,45 @@
         <v>3.64</v>
       </c>
       <c r="M52">
-        <v>1.190978</v>
+        <v>1.36262004</v>
       </c>
       <c r="N52">
-        <v>2.449022</v>
+        <v>2.27737996</v>
       </c>
       <c r="O52">
-        <v>0.4898044000000001</v>
+        <v>0.455475992</v>
       </c>
       <c r="P52">
-        <v>1.9592176</v>
+        <v>1.821903968</v>
       </c>
       <c r="Q52">
-        <v>4.0492176</v>
+        <v>3.911903968</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.226767181522323</v>
+        <v>0.2300500328878074</v>
       </c>
       <c r="T52">
-        <v>1.981664811760508</v>
+        <v>2.017613379774304</v>
       </c>
       <c r="U52">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.056311703490745</v>
+        <v>2.671324282006009</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1420597161150256</v>
+        <v>0.1419758414688897</v>
       </c>
       <c r="C53">
-        <v>20.5031686708693</v>
+        <v>20.16409332027412</v>
       </c>
       <c r="D53">
-        <v>37.2947686708693</v>
+        <v>37.32729332027412</v>
       </c>
       <c r="E53">
-        <v>10.3916</v>
+        <v>10.7632</v>
       </c>
       <c r="F53">
-        <v>18.9516</v>
+        <v>19.3232</v>
       </c>
       <c r="G53">
         <v>2.16</v>
@@ -5627,28 +5627,28 @@
         <v>3.64</v>
       </c>
       <c r="M53">
-        <v>1.36262004</v>
+        <v>1.38933808</v>
       </c>
       <c r="N53">
-        <v>2.27737996</v>
+        <v>2.25066192</v>
       </c>
       <c r="O53">
-        <v>0.455475992</v>
+        <v>0.450132384</v>
       </c>
       <c r="P53">
-        <v>1.821903968</v>
+        <v>1.800529536</v>
       </c>
       <c r="Q53">
-        <v>3.911903968</v>
+        <v>3.890529536</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2300500328878074</v>
+        <v>0.2334696697268535</v>
       </c>
       <c r="T53">
-        <v>2.017613379774304</v>
+        <v>2.055059804788675</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.671324282006009</v>
+        <v>2.619952661198201</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1419758414688897</v>
+        <v>0.1418919668227538</v>
       </c>
       <c r="C54">
-        <v>20.16409332027412</v>
+        <v>19.82507474848262</v>
       </c>
       <c r="D54">
-        <v>37.32729332027412</v>
+        <v>37.35987474848262</v>
       </c>
       <c r="E54">
-        <v>10.7632</v>
+        <v>11.1348</v>
       </c>
       <c r="F54">
-        <v>19.3232</v>
+        <v>19.6948</v>
       </c>
       <c r="G54">
         <v>2.16</v>
@@ -5709,28 +5709,28 @@
         <v>3.64</v>
       </c>
       <c r="M54">
-        <v>1.38933808</v>
+        <v>1.41605612</v>
       </c>
       <c r="N54">
-        <v>2.25066192</v>
+        <v>2.22394388</v>
       </c>
       <c r="O54">
-        <v>0.450132384</v>
+        <v>0.444788776</v>
       </c>
       <c r="P54">
-        <v>1.800529536</v>
+        <v>1.779155104</v>
       </c>
       <c r="Q54">
-        <v>3.890529536</v>
+        <v>3.869155104</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2334696697268535</v>
+        <v>0.2370348230271357</v>
       </c>
       <c r="T54">
-        <v>2.055059804788675</v>
+        <v>2.094099694697274</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.619952661198201</v>
+        <v>2.57051959211899</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1418919668227538</v>
+        <v>0.1418080921766179</v>
       </c>
       <c r="C55">
-        <v>19.82507474848262</v>
+        <v>19.4861131043042</v>
       </c>
       <c r="D55">
-        <v>37.35987474848262</v>
+        <v>37.3925131043042</v>
       </c>
       <c r="E55">
-        <v>11.1348</v>
+        <v>11.5064</v>
       </c>
       <c r="F55">
-        <v>19.6948</v>
+        <v>20.0664</v>
       </c>
       <c r="G55">
         <v>2.16</v>
@@ -5791,28 +5791,28 @@
         <v>3.64</v>
       </c>
       <c r="M55">
-        <v>1.41605612</v>
+        <v>1.44277416</v>
       </c>
       <c r="N55">
-        <v>2.22394388</v>
+        <v>2.19722584</v>
       </c>
       <c r="O55">
-        <v>0.444788776</v>
+        <v>0.439445168</v>
       </c>
       <c r="P55">
-        <v>1.779155104</v>
+        <v>1.757780672</v>
       </c>
       <c r="Q55">
-        <v>3.869155104</v>
+        <v>3.847780672</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2370348230271357</v>
+        <v>0.2407549829926475</v>
       </c>
       <c r="T55">
-        <v>2.094099694697274</v>
+        <v>2.134836971123639</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.57051959211899</v>
+        <v>2.52291737745012</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1418080921766179</v>
+        <v>0.1434402175304819</v>
       </c>
       <c r="C56">
-        <v>19.4861131043042</v>
+        <v>18.48947077824448</v>
       </c>
       <c r="D56">
-        <v>37.3925131043042</v>
+        <v>36.76747077824448</v>
       </c>
       <c r="E56">
-        <v>11.5064</v>
+        <v>11.878</v>
       </c>
       <c r="F56">
-        <v>20.0664</v>
+        <v>20.438</v>
       </c>
       <c r="G56">
         <v>2.16</v>
@@ -5873,45 +5873,45 @@
         <v>3.64</v>
       </c>
       <c r="M56">
-        <v>1.44277416</v>
+        <v>1.5492004</v>
       </c>
       <c r="N56">
-        <v>2.19722584</v>
+        <v>2.0907996</v>
       </c>
       <c r="O56">
-        <v>0.439445168</v>
+        <v>0.4181599199999999</v>
       </c>
       <c r="P56">
-        <v>1.757780672</v>
+        <v>1.67263968</v>
       </c>
       <c r="Q56">
-        <v>3.847780672</v>
+        <v>3.76263968</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2407549829926475</v>
+        <v>0.244640483401071</v>
       </c>
       <c r="T56">
-        <v>2.134836971123639</v>
+        <v>2.177384793168954</v>
       </c>
       <c r="U56">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V56">
         <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.52291737745012</v>
+        <v>2.349599186780483</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1434402175304819</v>
+        <v>0.143387542884346</v>
       </c>
       <c r="C57">
-        <v>18.48947077824448</v>
+        <v>18.13771668741806</v>
       </c>
       <c r="D57">
-        <v>36.76747077824448</v>
+        <v>36.78731668741807</v>
       </c>
       <c r="E57">
-        <v>11.878</v>
+        <v>12.2496</v>
       </c>
       <c r="F57">
-        <v>20.438</v>
+        <v>20.8096</v>
       </c>
       <c r="G57">
         <v>2.16</v>
@@ -5955,28 +5955,28 @@
         <v>3.64</v>
       </c>
       <c r="M57">
-        <v>1.5492004</v>
+        <v>1.57736768</v>
       </c>
       <c r="N57">
-        <v>2.0907996</v>
+        <v>2.06263232</v>
       </c>
       <c r="O57">
-        <v>0.4181599199999999</v>
+        <v>0.4125264639999999</v>
       </c>
       <c r="P57">
-        <v>1.67263968</v>
+        <v>1.650105856</v>
       </c>
       <c r="Q57">
-        <v>3.76263968</v>
+        <v>3.740105856</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.244640483401071</v>
+        <v>0.2487025974644228</v>
       </c>
       <c r="T57">
-        <v>2.177384793168954</v>
+        <v>2.221866607125418</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.349599186780483</v>
+        <v>2.307642058445118</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.143387542884346</v>
+        <v>0.1433348682382101</v>
       </c>
       <c r="C58">
-        <v>18.13771668741806</v>
+        <v>17.78598403254091</v>
       </c>
       <c r="D58">
-        <v>36.78731668741807</v>
+        <v>36.80718403254091</v>
       </c>
       <c r="E58">
-        <v>12.2496</v>
+        <v>12.6212</v>
       </c>
       <c r="F58">
-        <v>20.8096</v>
+        <v>21.1812</v>
       </c>
       <c r="G58">
         <v>2.16</v>
@@ -6037,28 +6037,28 @@
         <v>3.64</v>
       </c>
       <c r="M58">
-        <v>1.57736768</v>
+        <v>1.60553496</v>
       </c>
       <c r="N58">
-        <v>2.06263232</v>
+        <v>2.03446504</v>
       </c>
       <c r="O58">
-        <v>0.4125264639999999</v>
+        <v>0.4068930079999999</v>
       </c>
       <c r="P58">
-        <v>1.650105856</v>
+        <v>1.627572032</v>
       </c>
       <c r="Q58">
-        <v>3.740105856</v>
+        <v>3.717572032</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2487025974644228</v>
+        <v>0.2529536470656049</v>
       </c>
       <c r="T58">
-        <v>2.221866607125418</v>
+        <v>2.268417342661253</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.307642058445118</v>
+        <v>2.267157110051343</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1433348682382101</v>
+        <v>0.1432821935920742</v>
       </c>
       <c r="C59">
-        <v>17.78598403254091</v>
+        <v>17.43427284836186</v>
       </c>
       <c r="D59">
-        <v>36.80718403254091</v>
+        <v>36.82707284836186</v>
       </c>
       <c r="E59">
-        <v>12.6212</v>
+        <v>12.9928</v>
       </c>
       <c r="F59">
-        <v>21.1812</v>
+        <v>21.5528</v>
       </c>
       <c r="G59">
         <v>2.16</v>
@@ -6119,28 +6119,28 @@
         <v>3.64</v>
       </c>
       <c r="M59">
-        <v>1.60553496</v>
+        <v>1.633702240000001</v>
       </c>
       <c r="N59">
-        <v>2.03446504</v>
+        <v>2.00629776</v>
       </c>
       <c r="O59">
-        <v>0.4068930079999999</v>
+        <v>0.401259552</v>
       </c>
       <c r="P59">
-        <v>1.627572032</v>
+        <v>1.605038208</v>
       </c>
       <c r="Q59">
-        <v>3.717572032</v>
+        <v>3.695038208</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2529536470656049</v>
+        <v>0.2574071276001766</v>
       </c>
       <c r="T59">
-        <v>2.268417342661253</v>
+        <v>2.317184779889272</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.267157110051343</v>
+        <v>2.228068194360803</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1432821935920742</v>
+        <v>0.1432295189459383</v>
       </c>
       <c r="C60">
-        <v>17.43427284836186</v>
+        <v>17.08258316970485</v>
       </c>
       <c r="D60">
-        <v>36.82707284836186</v>
+        <v>36.84698316970486</v>
       </c>
       <c r="E60">
-        <v>12.9928</v>
+        <v>13.3644</v>
       </c>
       <c r="F60">
-        <v>21.5528</v>
+        <v>21.9244</v>
       </c>
       <c r="G60">
         <v>2.16</v>
@@ -6201,28 +6201,28 @@
         <v>3.64</v>
       </c>
       <c r="M60">
-        <v>1.63370224</v>
+        <v>1.66186952</v>
       </c>
       <c r="N60">
-        <v>2.00629776</v>
+        <v>1.97813048</v>
       </c>
       <c r="O60">
-        <v>0.401259552</v>
+        <v>0.395626096</v>
       </c>
       <c r="P60">
-        <v>1.605038208</v>
+        <v>1.582504384</v>
       </c>
       <c r="Q60">
-        <v>3.695038208</v>
+        <v>3.672504384</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2574071276001766</v>
+        <v>0.2620778510876544</v>
       </c>
       <c r="T60">
-        <v>2.317184779889271</v>
+        <v>2.368331116494266</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.228068194360803</v>
+        <v>2.190304326659772</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1432295189459383</v>
+        <v>0.1431768442998024</v>
       </c>
       <c r="C61">
-        <v>17.08258316970485</v>
+        <v>16.7309150314693</v>
       </c>
       <c r="D61">
-        <v>36.84698316970486</v>
+        <v>36.8669150314693</v>
       </c>
       <c r="E61">
-        <v>13.3644</v>
+        <v>13.736</v>
       </c>
       <c r="F61">
-        <v>21.9244</v>
+        <v>22.296</v>
       </c>
       <c r="G61">
         <v>2.16</v>
@@ -6283,28 +6283,28 @@
         <v>3.64</v>
       </c>
       <c r="M61">
-        <v>1.66186952</v>
+        <v>1.6900368</v>
       </c>
       <c r="N61">
-        <v>1.97813048</v>
+        <v>1.9499632</v>
       </c>
       <c r="O61">
-        <v>0.395626096</v>
+        <v>0.38999264</v>
       </c>
       <c r="P61">
-        <v>1.582504384</v>
+        <v>1.55997056</v>
       </c>
       <c r="Q61">
-        <v>3.672504384</v>
+        <v>3.64997056</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2620778510876544</v>
+        <v>0.2669821107495059</v>
       </c>
       <c r="T61">
-        <v>2.368331116494266</v>
+        <v>2.42203476992951</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.190304326659772</v>
+        <v>2.153799254548776</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1431768442998024</v>
+        <v>0.1431241696536664</v>
       </c>
       <c r="C62">
-        <v>16.7309150314693</v>
+        <v>16.37926846863005</v>
       </c>
       <c r="D62">
-        <v>36.8669150314693</v>
+        <v>36.88686846863005</v>
       </c>
       <c r="E62">
-        <v>13.736</v>
+        <v>14.1076</v>
       </c>
       <c r="F62">
-        <v>22.296</v>
+        <v>22.6676</v>
       </c>
       <c r="G62">
         <v>2.16</v>
@@ -6365,28 +6365,28 @@
         <v>3.64</v>
       </c>
       <c r="M62">
-        <v>1.6900368</v>
+        <v>1.71820408</v>
       </c>
       <c r="N62">
-        <v>1.9499632</v>
+        <v>1.92179592</v>
       </c>
       <c r="O62">
-        <v>0.38999264</v>
+        <v>0.384359184</v>
       </c>
       <c r="P62">
-        <v>1.55997056</v>
+        <v>1.537436736</v>
       </c>
       <c r="Q62">
-        <v>3.64997056</v>
+        <v>3.627436736</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2669821107495059</v>
+        <v>0.272137870906837</v>
       </c>
       <c r="T62">
-        <v>2.42203476992951</v>
+        <v>2.478492456874253</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.153799254548776</v>
+        <v>2.118491070047977</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1431241696536664</v>
+        <v>0.1430714950075305</v>
       </c>
       <c r="C63">
-        <v>16.37926846863005</v>
+        <v>16.02764351623774</v>
       </c>
       <c r="D63">
-        <v>36.88686846863005</v>
+        <v>36.90684351623774</v>
       </c>
       <c r="E63">
-        <v>14.1076</v>
+        <v>14.4792</v>
       </c>
       <c r="F63">
-        <v>22.6676</v>
+        <v>23.0392</v>
       </c>
       <c r="G63">
         <v>2.16</v>
@@ -6447,28 +6447,28 @@
         <v>3.64</v>
       </c>
       <c r="M63">
-        <v>1.71820408</v>
+        <v>1.74637136</v>
       </c>
       <c r="N63">
-        <v>1.92179592</v>
+        <v>1.89362864</v>
       </c>
       <c r="O63">
-        <v>0.384359184</v>
+        <v>0.378725728</v>
       </c>
       <c r="P63">
-        <v>1.537436736</v>
+        <v>1.514902912</v>
       </c>
       <c r="Q63">
-        <v>3.627436736</v>
+        <v>3.604902912</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.272137870906837</v>
+        <v>0.2775649868619224</v>
       </c>
       <c r="T63">
-        <v>2.478492456874253</v>
+        <v>2.537921601026615</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.118491070047977</v>
+        <v>2.084321859240752</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1430714950075305</v>
+        <v>0.1430188203613946</v>
       </c>
       <c r="C64">
-        <v>16.02764351623774</v>
+        <v>15.67604020941899</v>
       </c>
       <c r="D64">
-        <v>36.90684351623774</v>
+        <v>36.92684020941899</v>
       </c>
       <c r="E64">
-        <v>14.4792</v>
+        <v>14.8508</v>
       </c>
       <c r="F64">
-        <v>23.0392</v>
+        <v>23.4108</v>
       </c>
       <c r="G64">
         <v>2.16</v>
@@ -6529,28 +6529,28 @@
         <v>3.64</v>
       </c>
       <c r="M64">
-        <v>1.74637136</v>
+        <v>1.77453864</v>
       </c>
       <c r="N64">
-        <v>1.89362864</v>
+        <v>1.86546136</v>
       </c>
       <c r="O64">
-        <v>0.378725728</v>
+        <v>0.373092272</v>
       </c>
       <c r="P64">
-        <v>1.514902912</v>
+        <v>1.492369088</v>
       </c>
       <c r="Q64">
-        <v>3.604902912</v>
+        <v>3.582369088</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2775649868619224</v>
+        <v>0.2832854604362017</v>
       </c>
       <c r="T64">
-        <v>2.537921601026615</v>
+        <v>2.600563131349376</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.084321859240752</v>
+        <v>2.051237385284549</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1430188203613946</v>
+        <v>0.1429661457152587</v>
       </c>
       <c r="C65">
-        <v>15.67604020941899</v>
+        <v>15.32445858337662</v>
       </c>
       <c r="D65">
-        <v>36.92684020941899</v>
+        <v>36.94685858337662</v>
       </c>
       <c r="E65">
-        <v>14.8508</v>
+        <v>15.2224</v>
       </c>
       <c r="F65">
-        <v>23.4108</v>
+        <v>23.7824</v>
       </c>
       <c r="G65">
         <v>2.16</v>
@@ -6611,28 +6611,28 @@
         <v>3.64</v>
       </c>
       <c r="M65">
-        <v>1.77453864</v>
+        <v>1.80270592</v>
       </c>
       <c r="N65">
-        <v>1.86546136</v>
+        <v>1.83729408</v>
       </c>
       <c r="O65">
-        <v>0.373092272</v>
+        <v>0.367458816</v>
       </c>
       <c r="P65">
-        <v>1.492369088</v>
+        <v>1.469835264</v>
       </c>
       <c r="Q65">
-        <v>3.582369088</v>
+        <v>3.559835264</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2832854604362017</v>
+        <v>0.2893237380979408</v>
       </c>
       <c r="T65">
-        <v>2.600563131349376</v>
+        <v>2.666684746690066</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.051237385284549</v>
+        <v>2.019186801139478</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1429661457152587</v>
+        <v>0.1502974710691228</v>
       </c>
       <c r="C66">
-        <v>15.32445858337662</v>
+        <v>12.36074378570112</v>
       </c>
       <c r="D66">
-        <v>36.94685858337662</v>
+        <v>34.35474378570112</v>
       </c>
       <c r="E66">
-        <v>15.2224</v>
+        <v>15.594</v>
       </c>
       <c r="F66">
-        <v>23.7824</v>
+        <v>24.154</v>
       </c>
       <c r="G66">
         <v>2.16</v>
@@ -6693,45 +6693,45 @@
         <v>3.64</v>
       </c>
       <c r="M66">
-        <v>1.80270592</v>
+        <v>2.17386</v>
       </c>
       <c r="N66">
-        <v>1.83729408</v>
+        <v>1.46614</v>
       </c>
       <c r="O66">
-        <v>0.367458816</v>
+        <v>0.293228</v>
       </c>
       <c r="P66">
-        <v>1.469835264</v>
+        <v>1.172912</v>
       </c>
       <c r="Q66">
-        <v>3.559835264</v>
+        <v>3.262912</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2893237380979408</v>
+        <v>0.2957070601974937</v>
       </c>
       <c r="T66">
-        <v>2.666684746690066</v>
+        <v>2.736584740050225</v>
       </c>
       <c r="U66">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V66">
         <v>0.2</v>
       </c>
       <c r="W66">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.019186801139478</v>
+        <v>1.674440856356895</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1502974710691228</v>
+        <v>0.1503583964229869</v>
       </c>
       <c r="C67">
-        <v>12.36074378570112</v>
+        <v>11.96912554715062</v>
       </c>
       <c r="D67">
-        <v>34.35474378570112</v>
+        <v>34.33472554715062</v>
       </c>
       <c r="E67">
-        <v>15.594</v>
+        <v>15.9656</v>
       </c>
       <c r="F67">
-        <v>24.154</v>
+        <v>24.5256</v>
       </c>
       <c r="G67">
         <v>2.16</v>
@@ -6775,28 +6775,28 @@
         <v>3.64</v>
       </c>
       <c r="M67">
-        <v>2.17386</v>
+        <v>2.207304</v>
       </c>
       <c r="N67">
-        <v>1.46614</v>
+        <v>1.432696</v>
       </c>
       <c r="O67">
-        <v>0.293228</v>
+        <v>0.2865392</v>
       </c>
       <c r="P67">
-        <v>1.172912</v>
+        <v>1.1461568</v>
       </c>
       <c r="Q67">
-        <v>3.262912</v>
+        <v>3.2361568</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2957070601974937</v>
+        <v>0.3024658718323144</v>
       </c>
       <c r="T67">
-        <v>2.736584740050225</v>
+        <v>2.810596497725688</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.674440856356895</v>
+        <v>1.649070540351488</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1503583964229869</v>
+        <v>0.150419321776851</v>
       </c>
       <c r="C68">
-        <v>11.96912554715062</v>
+        <v>11.57753062395422</v>
       </c>
       <c r="D68">
-        <v>34.33472554715062</v>
+        <v>34.31473062395423</v>
       </c>
       <c r="E68">
-        <v>15.9656</v>
+        <v>16.3372</v>
       </c>
       <c r="F68">
-        <v>24.5256</v>
+        <v>24.89720000000001</v>
       </c>
       <c r="G68">
         <v>2.16</v>
@@ -6857,28 +6857,28 @@
         <v>3.64</v>
       </c>
       <c r="M68">
-        <v>2.207304</v>
+        <v>2.240748</v>
       </c>
       <c r="N68">
-        <v>1.432696</v>
+        <v>1.399252</v>
       </c>
       <c r="O68">
-        <v>0.2865392</v>
+        <v>0.2798503999999999</v>
       </c>
       <c r="P68">
-        <v>1.1461568</v>
+        <v>1.1194016</v>
       </c>
       <c r="Q68">
-        <v>3.2361568</v>
+        <v>3.2094016</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3024658718323144</v>
+        <v>0.3096343084147</v>
       </c>
       <c r="T68">
-        <v>2.810596497725688</v>
+        <v>2.889093816472391</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.649070540351488</v>
+        <v>1.624457547211913</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.150419321776851</v>
+        <v>0.150480247130715</v>
       </c>
       <c r="C69">
-        <v>11.57753062395422</v>
+        <v>11.18595897540238</v>
       </c>
       <c r="D69">
-        <v>34.31473062395423</v>
+        <v>34.29475897540238</v>
       </c>
       <c r="E69">
-        <v>16.3372</v>
+        <v>16.7088</v>
       </c>
       <c r="F69">
-        <v>24.89720000000001</v>
+        <v>25.26880000000001</v>
       </c>
       <c r="G69">
         <v>2.16</v>
@@ -6939,28 +6939,28 @@
         <v>3.64</v>
       </c>
       <c r="M69">
-        <v>2.240748</v>
+        <v>2.274192000000001</v>
       </c>
       <c r="N69">
-        <v>1.399252</v>
+        <v>1.365807999999999</v>
       </c>
       <c r="O69">
-        <v>0.2798503999999999</v>
+        <v>0.2731615999999999</v>
       </c>
       <c r="P69">
-        <v>1.1194016</v>
+        <v>1.0926464</v>
       </c>
       <c r="Q69">
-        <v>3.2094016</v>
+        <v>3.1826464</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3096343084147</v>
+        <v>0.3172507722834845</v>
       </c>
       <c r="T69">
-        <v>2.889093816472391</v>
+        <v>2.972497217640762</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.624457547211913</v>
+        <v>1.600568465635267</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.150480247130715</v>
+        <v>0.1505411724845792</v>
       </c>
       <c r="C70">
-        <v>11.18595897540238</v>
+        <v>10.79441056088021</v>
       </c>
       <c r="D70">
-        <v>34.29475897540238</v>
+        <v>34.2748105608802</v>
       </c>
       <c r="E70">
-        <v>16.7088</v>
+        <v>17.0804</v>
       </c>
       <c r="F70">
-        <v>25.26880000000001</v>
+        <v>25.6404</v>
       </c>
       <c r="G70">
         <v>2.16</v>
@@ -7021,28 +7021,28 @@
         <v>3.64</v>
       </c>
       <c r="M70">
-        <v>2.274192000000001</v>
+        <v>2.307636</v>
       </c>
       <c r="N70">
-        <v>1.365807999999999</v>
+        <v>1.332364</v>
       </c>
       <c r="O70">
-        <v>0.2731615999999999</v>
+        <v>0.2664728</v>
       </c>
       <c r="P70">
-        <v>1.0926464</v>
+        <v>1.0658912</v>
       </c>
       <c r="Q70">
-        <v>3.1826464</v>
+        <v>3.1558912</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3172507722834845</v>
+        <v>0.3253586209179973</v>
       </c>
       <c r="T70">
-        <v>2.972497217640762</v>
+        <v>3.061281483400642</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.600568465635267</v>
+        <v>1.577371821205771</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1505411724845792</v>
+        <v>0.1506020978384432</v>
       </c>
       <c r="C71">
-        <v>10.79441056088021</v>
+        <v>10.40288533986732</v>
       </c>
       <c r="D71">
-        <v>34.2748105608802</v>
+        <v>34.25488533986733</v>
       </c>
       <c r="E71">
-        <v>17.0804</v>
+        <v>17.45200000000001</v>
       </c>
       <c r="F71">
-        <v>25.6404</v>
+        <v>26.012</v>
       </c>
       <c r="G71">
         <v>2.16</v>
@@ -7103,28 +7103,28 @@
         <v>3.64</v>
       </c>
       <c r="M71">
-        <v>2.307636</v>
+        <v>2.34108</v>
       </c>
       <c r="N71">
-        <v>1.332364</v>
+        <v>1.29892</v>
       </c>
       <c r="O71">
-        <v>0.2664728</v>
+        <v>0.259784</v>
       </c>
       <c r="P71">
-        <v>1.0658912</v>
+        <v>1.039136</v>
       </c>
       <c r="Q71">
-        <v>3.1558912</v>
+        <v>3.129136</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3253586209179973</v>
+        <v>0.3340069927948108</v>
       </c>
       <c r="T71">
-        <v>3.061281483400642</v>
+        <v>3.15598470021118</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.577371821205771</v>
+        <v>1.554837938045688</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1506020978384432</v>
+        <v>0.1506630231923073</v>
       </c>
       <c r="C72">
-        <v>10.40288533986732</v>
+        <v>10.01138327193744</v>
       </c>
       <c r="D72">
-        <v>34.25488533986733</v>
+        <v>34.23498327193745</v>
       </c>
       <c r="E72">
-        <v>17.45200000000001</v>
+        <v>17.82360000000001</v>
       </c>
       <c r="F72">
-        <v>26.012</v>
+        <v>26.3836</v>
       </c>
       <c r="G72">
         <v>2.16</v>
@@ -7185,28 +7185,28 @@
         <v>3.64</v>
       </c>
       <c r="M72">
-        <v>2.34108</v>
+        <v>2.374524000000001</v>
       </c>
       <c r="N72">
-        <v>1.29892</v>
+        <v>1.265476</v>
       </c>
       <c r="O72">
-        <v>0.259784</v>
+        <v>0.2530951999999999</v>
       </c>
       <c r="P72">
-        <v>1.039136</v>
+        <v>1.0123808</v>
       </c>
       <c r="Q72">
-        <v>3.129136</v>
+        <v>3.1023808</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3340069927948108</v>
+        <v>0.3432518041114046</v>
       </c>
       <c r="T72">
-        <v>3.15598470021118</v>
+        <v>3.25721917335348</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.554837938045688</v>
+        <v>1.532938812157721</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1506630231923073</v>
+        <v>0.1507239485461714</v>
       </c>
       <c r="C73">
-        <v>10.01138327193745</v>
+        <v>9.619904316758252</v>
       </c>
       <c r="D73">
-        <v>34.23498327193744</v>
+        <v>34.21510431675825</v>
       </c>
       <c r="E73">
-        <v>17.8236</v>
+        <v>18.1952</v>
       </c>
       <c r="F73">
-        <v>26.3836</v>
+        <v>26.7552</v>
       </c>
       <c r="G73">
         <v>2.16</v>
@@ -7267,28 +7267,28 @@
         <v>3.64</v>
       </c>
       <c r="M73">
-        <v>2.374524</v>
+        <v>2.407968</v>
       </c>
       <c r="N73">
-        <v>1.265476</v>
+        <v>1.232032</v>
       </c>
       <c r="O73">
-        <v>0.2530952</v>
+        <v>0.2464064000000001</v>
       </c>
       <c r="P73">
-        <v>1.0123808</v>
+        <v>0.9856256000000002</v>
       </c>
       <c r="Q73">
-        <v>3.102380800000001</v>
+        <v>3.0756256</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3432518041114045</v>
+        <v>0.3531569590934692</v>
       </c>
       <c r="T73">
-        <v>3.257219173353478</v>
+        <v>3.365684680291656</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.532938812157721</v>
+        <v>1.511647995322197</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1507239485461714</v>
+        <v>0.1870593182120369</v>
       </c>
       <c r="C74">
-        <v>9.619904316758252</v>
+        <v>0.4473382690570062</v>
       </c>
       <c r="D74">
-        <v>34.21510431675825</v>
+        <v>25.41413826905701</v>
       </c>
       <c r="E74">
-        <v>18.1952</v>
+        <v>18.5668</v>
       </c>
       <c r="F74">
-        <v>26.7552</v>
+        <v>27.1268</v>
       </c>
       <c r="G74">
         <v>2.16</v>
@@ -7349,45 +7349,45 @@
         <v>3.64</v>
       </c>
       <c r="M74">
-        <v>2.407968</v>
+        <v>3.982214240000001</v>
       </c>
       <c r="N74">
-        <v>1.232032</v>
+        <v>-0.3422142400000006</v>
       </c>
       <c r="O74">
-        <v>0.2464064000000001</v>
+        <v>-0.06844284800000011</v>
       </c>
       <c r="P74">
-        <v>0.9856256000000002</v>
+        <v>-0.2737713920000004</v>
       </c>
       <c r="Q74">
-        <v>3.0756256</v>
+        <v>1.816228608</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3531569590934692</v>
+        <v>0.3684676897459724</v>
       </c>
       <c r="T74">
-        <v>3.365684680291656</v>
+        <v>3.533343456436467</v>
       </c>
       <c r="U74">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2</v>
+        <v>0.1828128664418617</v>
       </c>
       <c r="W74">
-        <v>0.07199999999999999</v>
+        <v>0.1199630712063347</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.511647995322197</v>
+        <v>0.9140643322093086</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1870593182120369</v>
+        <v>0.1880693182120369</v>
       </c>
       <c r="C75">
-        <v>0.4473382690570062</v>
+        <v>-0.1046820771872241</v>
       </c>
       <c r="D75">
-        <v>25.41413826905701</v>
+        <v>25.23371792281278</v>
       </c>
       <c r="E75">
-        <v>18.5668</v>
+        <v>18.9384</v>
       </c>
       <c r="F75">
-        <v>27.1268</v>
+        <v>27.4984</v>
       </c>
       <c r="G75">
         <v>2.16</v>
@@ -7431,37 +7431,37 @@
         <v>3.64</v>
       </c>
       <c r="M75">
-        <v>3.982214240000001</v>
+        <v>4.036765120000001</v>
       </c>
       <c r="N75">
-        <v>-0.3422142400000006</v>
+        <v>-0.3967651200000009</v>
       </c>
       <c r="O75">
-        <v>-0.06844284800000011</v>
+        <v>-0.07935302400000017</v>
       </c>
       <c r="P75">
-        <v>-0.2737713920000004</v>
+        <v>-0.3174120960000007</v>
       </c>
       <c r="Q75">
-        <v>1.816228608</v>
+        <v>1.772587904</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3684676897459724</v>
+        <v>0.3808779855054328</v>
       </c>
       <c r="T75">
-        <v>3.533343456436467</v>
+        <v>3.669241281684023</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1828128664418617</v>
+        <v>0.1803424223007555</v>
       </c>
       <c r="W75">
-        <v>0.1199630712063347</v>
+        <v>0.1203257324062491</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9140643322093086</v>
+        <v>0.9017121115037774</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1880693182120369</v>
+        <v>0.1890793182120369</v>
       </c>
       <c r="C76">
-        <v>-0.1046820771872241</v>
+        <v>-0.6541587967311102</v>
       </c>
       <c r="D76">
-        <v>25.23371792281278</v>
+        <v>25.05584120326889</v>
       </c>
       <c r="E76">
-        <v>18.9384</v>
+        <v>19.31</v>
       </c>
       <c r="F76">
-        <v>27.4984</v>
+        <v>27.87</v>
       </c>
       <c r="G76">
         <v>2.16</v>
@@ -7513,37 +7513,37 @@
         <v>3.64</v>
       </c>
       <c r="M76">
-        <v>4.036765120000001</v>
+        <v>4.091316000000001</v>
       </c>
       <c r="N76">
-        <v>-0.3967651200000009</v>
+        <v>-0.4513160000000007</v>
       </c>
       <c r="O76">
-        <v>-0.07935302400000017</v>
+        <v>-0.09026320000000015</v>
       </c>
       <c r="P76">
-        <v>-0.3174120960000007</v>
+        <v>-0.3610528000000006</v>
       </c>
       <c r="Q76">
-        <v>1.772587904</v>
+        <v>1.7289472</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3808779855054328</v>
+        <v>0.3942811049256502</v>
       </c>
       <c r="T76">
-        <v>3.669241281684023</v>
+        <v>3.816010932951384</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1803424223007555</v>
+        <v>0.1779378566700787</v>
       </c>
       <c r="W76">
-        <v>0.1203257324062491</v>
+        <v>0.1206787226408324</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9017121115037774</v>
+        <v>0.8896892833503938</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1890793182120369</v>
+        <v>0.1900893182120369</v>
       </c>
       <c r="C77">
-        <v>-0.6541587967311102</v>
+        <v>-1.201145304401155</v>
       </c>
       <c r="D77">
-        <v>25.05584120326889</v>
+        <v>24.88045469559885</v>
       </c>
       <c r="E77">
-        <v>19.31</v>
+        <v>19.6816</v>
       </c>
       <c r="F77">
-        <v>27.87</v>
+        <v>28.2416</v>
       </c>
       <c r="G77">
         <v>2.16</v>
@@ -7595,37 +7595,37 @@
         <v>3.64</v>
       </c>
       <c r="M77">
-        <v>4.091316000000001</v>
+        <v>4.145866880000001</v>
       </c>
       <c r="N77">
-        <v>-0.4513160000000007</v>
+        <v>-0.5058668800000006</v>
       </c>
       <c r="O77">
-        <v>-0.09026320000000015</v>
+        <v>-0.1011733760000001</v>
       </c>
       <c r="P77">
-        <v>-0.3610528000000006</v>
+        <v>-0.4046935040000005</v>
       </c>
       <c r="Q77">
-        <v>1.7289472</v>
+        <v>1.685306496</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3942811049256502</v>
+        <v>0.4088011509642189</v>
       </c>
       <c r="T77">
-        <v>3.816010932951384</v>
+        <v>3.975011388491025</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1779378566700787</v>
+        <v>0.1755965690823146</v>
       </c>
       <c r="W77">
-        <v>0.1206787226408324</v>
+        <v>0.1210224236587162</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8896892833503938</v>
+        <v>0.8779828454115728</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1900893182120369</v>
+        <v>0.1910993182120369</v>
       </c>
       <c r="C78">
-        <v>-1.201145304401155</v>
+        <v>-1.745693529842136</v>
       </c>
       <c r="D78">
-        <v>24.88045469559885</v>
+        <v>24.70750647015787</v>
       </c>
       <c r="E78">
-        <v>19.6816</v>
+        <v>20.0532</v>
       </c>
       <c r="F78">
-        <v>28.2416</v>
+        <v>28.6132</v>
       </c>
       <c r="G78">
         <v>2.16</v>
@@ -7677,37 +7677,37 @@
         <v>3.64</v>
       </c>
       <c r="M78">
-        <v>4.145866880000001</v>
+        <v>4.200417760000001</v>
       </c>
       <c r="N78">
-        <v>-0.5058668800000006</v>
+        <v>-0.5604177600000004</v>
       </c>
       <c r="O78">
-        <v>-0.1011733760000001</v>
+        <v>-0.1120835520000001</v>
       </c>
       <c r="P78">
-        <v>-0.4046935040000005</v>
+        <v>-0.4483342080000003</v>
       </c>
       <c r="Q78">
-        <v>1.685306496</v>
+        <v>1.641665792</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4088011509642189</v>
+        <v>0.4245838097017938</v>
       </c>
       <c r="T78">
-        <v>3.975011388491025</v>
+        <v>4.147837970599332</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1755965690823146</v>
+        <v>0.1733160941591676</v>
       </c>
       <c r="W78">
-        <v>0.1210224236587162</v>
+        <v>0.1213571973774342</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8779828454115728</v>
+        <v>0.8665804707958381</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1910993182120369</v>
+        <v>0.1921093182120369</v>
       </c>
       <c r="C79">
-        <v>-1.745693529842136</v>
+        <v>-2.287853968779409</v>
       </c>
       <c r="D79">
-        <v>24.70750647015787</v>
+        <v>24.53694603122059</v>
       </c>
       <c r="E79">
-        <v>20.0532</v>
+        <v>20.4248</v>
       </c>
       <c r="F79">
-        <v>28.6132</v>
+        <v>28.9848</v>
       </c>
       <c r="G79">
         <v>2.16</v>
@@ -7759,37 +7759,37 @@
         <v>3.64</v>
       </c>
       <c r="M79">
-        <v>4.200417760000001</v>
+        <v>4.254968640000001</v>
       </c>
       <c r="N79">
-        <v>-0.5604177600000004</v>
+        <v>-0.6149686400000012</v>
       </c>
       <c r="O79">
-        <v>-0.1120835520000001</v>
+        <v>-0.1229937280000002</v>
       </c>
       <c r="P79">
-        <v>-0.4483342080000003</v>
+        <v>-0.4919749120000009</v>
       </c>
       <c r="Q79">
-        <v>1.641665792</v>
+        <v>1.598025087999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4245838097017938</v>
+        <v>0.4418012555973297</v>
       </c>
       <c r="T79">
-        <v>4.147837970599332</v>
+        <v>4.336376060172028</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1733160941591676</v>
+        <v>0.1710940929519988</v>
       </c>
       <c r="W79">
-        <v>0.1213571973774342</v>
+        <v>0.1216833871546466</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8665804707958381</v>
+        <v>0.8554704647599939</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1921093182120369</v>
+        <v>0.1931193182120369</v>
       </c>
       <c r="C80">
-        <v>-2.287853968779409</v>
+        <v>-2.827675732172754</v>
       </c>
       <c r="D80">
-        <v>24.53694603122059</v>
+        <v>24.36872426782725</v>
       </c>
       <c r="E80">
-        <v>20.4248</v>
+        <v>20.79640000000001</v>
       </c>
       <c r="F80">
-        <v>28.9848</v>
+        <v>29.3564</v>
       </c>
       <c r="G80">
         <v>2.16</v>
@@ -7841,37 +7841,37 @@
         <v>3.64</v>
       </c>
       <c r="M80">
-        <v>4.254968640000001</v>
+        <v>4.309519520000001</v>
       </c>
       <c r="N80">
-        <v>-0.6149686400000012</v>
+        <v>-0.669519520000001</v>
       </c>
       <c r="O80">
-        <v>-0.1229937280000002</v>
+        <v>-0.1339039040000002</v>
       </c>
       <c r="P80">
-        <v>-0.4919749120000009</v>
+        <v>-0.5356156160000008</v>
       </c>
       <c r="Q80">
-        <v>1.598025087999999</v>
+        <v>1.554384384</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4418012555973297</v>
+        <v>0.4606584582448218</v>
       </c>
       <c r="T80">
-        <v>4.336376060172028</v>
+        <v>4.542870158275459</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1710940929519988</v>
+        <v>0.1689283449399482</v>
       </c>
       <c r="W80">
-        <v>0.1216833871546466</v>
+        <v>0.1220013189628156</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8554704647599939</v>
+        <v>0.8446417246997409</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1931193182120369</v>
+        <v>0.1941293182120369</v>
       </c>
       <c r="C81">
-        <v>-2.827675732172754</v>
+        <v>-3.365206593361783</v>
       </c>
       <c r="D81">
-        <v>24.36872426782725</v>
+        <v>24.20279340663822</v>
       </c>
       <c r="E81">
-        <v>20.79640000000001</v>
+        <v>21.16800000000001</v>
       </c>
       <c r="F81">
-        <v>29.3564</v>
+        <v>29.72800000000001</v>
       </c>
       <c r="G81">
         <v>2.16</v>
@@ -7923,37 +7923,37 @@
         <v>3.64</v>
       </c>
       <c r="M81">
-        <v>4.309519520000001</v>
+        <v>4.364070400000001</v>
       </c>
       <c r="N81">
-        <v>-0.669519520000001</v>
+        <v>-0.7240704000000009</v>
       </c>
       <c r="O81">
-        <v>-0.1339039040000002</v>
+        <v>-0.1448140800000002</v>
       </c>
       <c r="P81">
-        <v>-0.5356156160000008</v>
+        <v>-0.5792563200000007</v>
       </c>
       <c r="Q81">
-        <v>1.554384384</v>
+        <v>1.51074368</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4606584582448218</v>
+        <v>0.4814013811570628</v>
       </c>
       <c r="T81">
-        <v>4.542870158275459</v>
+        <v>4.770013666189231</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1689283449399482</v>
+        <v>0.1668167406281988</v>
       </c>
       <c r="W81">
-        <v>0.1220013189628156</v>
+        <v>0.1223113024757804</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8446417246997409</v>
+        <v>0.8340837031409941</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1941293182120369</v>
+        <v>0.1951393182120368</v>
       </c>
       <c r="C82">
-        <v>-3.365206593361783</v>
+        <v>-3.900493033298492</v>
       </c>
       <c r="D82">
-        <v>24.20279340663822</v>
+        <v>24.03910696670151</v>
       </c>
       <c r="E82">
-        <v>21.16800000000001</v>
+        <v>21.53960000000001</v>
       </c>
       <c r="F82">
-        <v>29.72800000000001</v>
+        <v>30.09960000000001</v>
       </c>
       <c r="G82">
         <v>2.16</v>
@@ -8005,37 +8005,37 @@
         <v>3.64</v>
       </c>
       <c r="M82">
-        <v>4.364070400000001</v>
+        <v>4.418621280000001</v>
       </c>
       <c r="N82">
-        <v>-0.7240704000000009</v>
+        <v>-0.7786212800000007</v>
       </c>
       <c r="O82">
-        <v>-0.1448140800000002</v>
+        <v>-0.1557242560000002</v>
       </c>
       <c r="P82">
-        <v>-0.5792563200000007</v>
+        <v>-0.6228970240000006</v>
       </c>
       <c r="Q82">
-        <v>1.51074368</v>
+        <v>1.467102976</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4814013811570628</v>
+        <v>0.5043277696390134</v>
       </c>
       <c r="T82">
-        <v>4.770013666189231</v>
+        <v>5.021067017041296</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1668167406281988</v>
+        <v>0.1647572746945174</v>
       </c>
       <c r="W82">
-        <v>0.1223113024757804</v>
+        <v>0.1226136320748449</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8340837031409941</v>
+        <v>0.8237863734725868</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1951393182120368</v>
+        <v>0.1961493182120369</v>
       </c>
       <c r="C83">
-        <v>-3.900493033298492</v>
+        <v>-4.433580283956513</v>
       </c>
       <c r="D83">
-        <v>24.03910696670151</v>
+        <v>23.87761971604349</v>
       </c>
       <c r="E83">
-        <v>21.53960000000001</v>
+        <v>21.91120000000001</v>
       </c>
       <c r="F83">
-        <v>30.09960000000001</v>
+        <v>30.47120000000001</v>
       </c>
       <c r="G83">
         <v>2.16</v>
@@ -8087,37 +8087,37 @@
         <v>3.64</v>
       </c>
       <c r="M83">
-        <v>4.418621280000001</v>
+        <v>4.473172160000002</v>
       </c>
       <c r="N83">
-        <v>-0.7786212800000007</v>
+        <v>-0.8331721600000015</v>
       </c>
       <c r="O83">
-        <v>-0.1557242560000002</v>
+        <v>-0.1666344320000003</v>
       </c>
       <c r="P83">
-        <v>-0.6228970240000006</v>
+        <v>-0.6665377280000012</v>
       </c>
       <c r="Q83">
-        <v>1.467102976</v>
+        <v>1.423462271999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5043277696390134</v>
+        <v>0.5298015346189587</v>
       </c>
       <c r="T83">
-        <v>5.021067017041296</v>
+        <v>5.300015184654702</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1647572746945174</v>
+        <v>0.1627480396372671</v>
       </c>
       <c r="W83">
-        <v>0.1226136320748449</v>
+        <v>0.1229085877812492</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8237863734725868</v>
+        <v>0.8137401981863356</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1961493182120369</v>
+        <v>0.1971593182120369</v>
       </c>
       <c r="C84">
-        <v>-4.433580283956513</v>
+        <v>-4.964512370002385</v>
       </c>
       <c r="D84">
-        <v>23.87761971604349</v>
+        <v>23.71828762999762</v>
       </c>
       <c r="E84">
-        <v>21.91120000000001</v>
+        <v>22.2828</v>
       </c>
       <c r="F84">
-        <v>30.47120000000001</v>
+        <v>30.8428</v>
       </c>
       <c r="G84">
         <v>2.16</v>
@@ -8169,37 +8169,37 @@
         <v>3.64</v>
       </c>
       <c r="M84">
-        <v>4.473172160000002</v>
+        <v>4.527723040000001</v>
       </c>
       <c r="N84">
-        <v>-0.8331721600000015</v>
+        <v>-0.8877230400000005</v>
       </c>
       <c r="O84">
-        <v>-0.1666344320000003</v>
+        <v>-0.1775446080000001</v>
       </c>
       <c r="P84">
-        <v>-0.6665377280000012</v>
+        <v>-0.7101784320000004</v>
       </c>
       <c r="Q84">
-        <v>1.423462271999999</v>
+        <v>1.379821568</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5298015346189587</v>
+        <v>0.5582722131259563</v>
       </c>
       <c r="T84">
-        <v>5.300015184654702</v>
+        <v>5.611780783752038</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1627480396372671</v>
+        <v>0.1607872198826013</v>
       </c>
       <c r="W84">
-        <v>0.1229085877812492</v>
+        <v>0.1231964361212342</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8137401981863356</v>
+        <v>0.8039360994130065</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1971593182120369</v>
+        <v>0.2471374881780399</v>
       </c>
       <c r="C85">
-        <v>-4.964512370002385</v>
+        <v>-11.22372237845912</v>
       </c>
       <c r="D85">
-        <v>23.71828762999762</v>
+        <v>17.83067762154089</v>
       </c>
       <c r="E85">
-        <v>22.2828</v>
+        <v>22.6544</v>
       </c>
       <c r="F85">
-        <v>30.8428</v>
+        <v>31.2144</v>
       </c>
       <c r="G85">
         <v>2.16</v>
@@ -8251,45 +8251,45 @@
         <v>3.64</v>
       </c>
       <c r="M85">
-        <v>4.527723040000001</v>
+        <v>6.267851520000002</v>
       </c>
       <c r="N85">
-        <v>-0.8877230400000005</v>
+        <v>-2.627851520000001</v>
       </c>
       <c r="O85">
-        <v>-0.1775446080000001</v>
+        <v>-0.5255703040000003</v>
       </c>
       <c r="P85">
-        <v>-0.7101784320000004</v>
+        <v>-2.102281216000001</v>
       </c>
       <c r="Q85">
-        <v>1.379821568</v>
+        <v>-0.01228121600000076</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5582722131259563</v>
+        <v>0.6128527887338477</v>
       </c>
       <c r="T85">
-        <v>5.611780783752038</v>
+        <v>6.209460457922409</v>
       </c>
       <c r="U85">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1607872198826013</v>
+        <v>0.1161482523440504</v>
       </c>
       <c r="W85">
-        <v>0.1231964361212342</v>
+        <v>0.1774774309293147</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.8039360994130065</v>
+        <v>0.580741261720252</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2471374881780399</v>
+        <v>0.2486874881780399</v>
       </c>
       <c r="C86">
-        <v>-11.22372237845912</v>
+        <v>-11.73154344640952</v>
       </c>
       <c r="D86">
-        <v>17.83067762154089</v>
+        <v>17.69445655359048</v>
       </c>
       <c r="E86">
-        <v>22.6544</v>
+        <v>23.026</v>
       </c>
       <c r="F86">
-        <v>31.2144</v>
+        <v>31.586</v>
       </c>
       <c r="G86">
         <v>2.16</v>
@@ -8333,37 +8333,37 @@
         <v>3.64</v>
       </c>
       <c r="M86">
-        <v>6.267851520000001</v>
+        <v>6.342468800000001</v>
       </c>
       <c r="N86">
-        <v>-2.627851520000001</v>
+        <v>-2.702468800000001</v>
       </c>
       <c r="O86">
-        <v>-0.5255703040000002</v>
+        <v>-0.5404937600000002</v>
       </c>
       <c r="P86">
-        <v>-2.102281216000001</v>
+        <v>-2.161975040000001</v>
       </c>
       <c r="Q86">
-        <v>-0.01228121600000032</v>
+        <v>-0.07197504000000032</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6128527887338473</v>
+        <v>0.6506563079827705</v>
       </c>
       <c r="T86">
-        <v>6.209460457922404</v>
+        <v>6.623424488450565</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1161482523440504</v>
+        <v>0.1147818023164733</v>
       </c>
       <c r="W86">
-        <v>0.1774774309293147</v>
+        <v>0.1777518140948522</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5807412617202521</v>
+        <v>0.5739090115823667</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2486874881780399</v>
+        <v>0.2502374881780399</v>
       </c>
       <c r="C87">
-        <v>-11.73154344640952</v>
+        <v>-12.23729891810159</v>
       </c>
       <c r="D87">
-        <v>17.69445655359048</v>
+        <v>17.56030108189841</v>
       </c>
       <c r="E87">
-        <v>23.026</v>
+        <v>23.3976</v>
       </c>
       <c r="F87">
-        <v>31.586</v>
+        <v>31.9576</v>
       </c>
       <c r="G87">
         <v>2.16</v>
@@ -8415,37 +8415,37 @@
         <v>3.64</v>
       </c>
       <c r="M87">
-        <v>6.342468800000001</v>
+        <v>6.417086080000001</v>
       </c>
       <c r="N87">
-        <v>-2.702468800000001</v>
+        <v>-2.777086080000001</v>
       </c>
       <c r="O87">
-        <v>-0.5404937600000002</v>
+        <v>-0.5554172160000002</v>
       </c>
       <c r="P87">
-        <v>-2.161975040000001</v>
+        <v>-2.221668864000001</v>
       </c>
       <c r="Q87">
-        <v>-0.07197504000000032</v>
+        <v>-0.1316688640000003</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6506563079827705</v>
+        <v>0.6938603299815399</v>
       </c>
       <c r="T87">
-        <v>6.623424488450565</v>
+        <v>7.096526237625606</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1147818023164733</v>
+        <v>0.1134471301965144</v>
       </c>
       <c r="W87">
-        <v>0.1777518140948522</v>
+        <v>0.1780198162565399</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5739090115823667</v>
+        <v>0.5672356509825718</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2502374881780399</v>
+        <v>0.2517874881780399</v>
       </c>
       <c r="C88">
-        <v>-12.23729891810159</v>
+        <v>-12.74103542269072</v>
       </c>
       <c r="D88">
-        <v>17.56030108189841</v>
+        <v>17.42816457730928</v>
       </c>
       <c r="E88">
-        <v>23.3976</v>
+        <v>23.7692</v>
       </c>
       <c r="F88">
-        <v>31.9576</v>
+        <v>32.3292</v>
       </c>
       <c r="G88">
         <v>2.16</v>
@@ -8497,37 +8497,37 @@
         <v>3.64</v>
       </c>
       <c r="M88">
-        <v>6.417086080000001</v>
+        <v>6.49170336</v>
       </c>
       <c r="N88">
-        <v>-2.777086080000001</v>
+        <v>-2.85170336</v>
       </c>
       <c r="O88">
-        <v>-0.5554172160000002</v>
+        <v>-0.5703406719999999</v>
       </c>
       <c r="P88">
-        <v>-2.221668864000001</v>
+        <v>-2.281362688</v>
       </c>
       <c r="Q88">
-        <v>-0.1316688640000003</v>
+        <v>-0.1913626879999994</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6938603299815399</v>
+        <v>0.7437111245955044</v>
       </c>
       <c r="T88">
-        <v>7.096526237625606</v>
+        <v>7.642412871289113</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1134471301965144</v>
+        <v>0.1121431401942556</v>
       </c>
       <c r="W88">
-        <v>0.1780198162565399</v>
+        <v>0.1782816574489935</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5672356509825718</v>
+        <v>0.560715700971278</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2517874881780399</v>
+        <v>0.2533374881780399</v>
       </c>
       <c r="C89">
-        <v>-12.74103542269072</v>
+        <v>-13.24279819632734</v>
       </c>
       <c r="D89">
-        <v>17.42816457730928</v>
+        <v>17.29800180367267</v>
       </c>
       <c r="E89">
-        <v>23.7692</v>
+        <v>24.1408</v>
       </c>
       <c r="F89">
-        <v>32.3292</v>
+        <v>32.7008</v>
       </c>
       <c r="G89">
         <v>2.16</v>
@@ -8579,37 +8579,37 @@
         <v>3.64</v>
       </c>
       <c r="M89">
-        <v>6.49170336</v>
+        <v>6.566320640000001</v>
       </c>
       <c r="N89">
-        <v>-2.85170336</v>
+        <v>-2.926320640000001</v>
       </c>
       <c r="O89">
-        <v>-0.5703406719999999</v>
+        <v>-0.5852641280000002</v>
       </c>
       <c r="P89">
-        <v>-2.281362688</v>
+        <v>-2.341056512000001</v>
       </c>
       <c r="Q89">
-        <v>-0.1913626879999994</v>
+        <v>-0.2510565120000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7437111245955044</v>
+        <v>0.8018703849784632</v>
       </c>
       <c r="T89">
-        <v>7.642412871289113</v>
+        <v>8.279280610563207</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1121431401942556</v>
+        <v>0.1108687863284118</v>
       </c>
       <c r="W89">
-        <v>0.1782816574489935</v>
+        <v>0.1785375477052549</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.560715700971278</v>
+        <v>0.5543439316420589</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2533374881780399</v>
+        <v>0.2548874881780399</v>
       </c>
       <c r="C90">
-        <v>-13.24279819632734</v>
+        <v>-13.74263113378968</v>
       </c>
       <c r="D90">
-        <v>17.29800180367267</v>
+        <v>17.16976886621033</v>
       </c>
       <c r="E90">
-        <v>24.1408</v>
+        <v>24.5124</v>
       </c>
       <c r="F90">
-        <v>32.7008</v>
+        <v>33.0724</v>
       </c>
       <c r="G90">
         <v>2.16</v>
@@ -8661,37 +8661,37 @@
         <v>3.64</v>
       </c>
       <c r="M90">
-        <v>6.566320640000001</v>
+        <v>6.640937920000001</v>
       </c>
       <c r="N90">
-        <v>-2.926320640000001</v>
+        <v>-3.000937920000001</v>
       </c>
       <c r="O90">
-        <v>-0.5852641280000002</v>
+        <v>-0.6001875840000002</v>
       </c>
       <c r="P90">
-        <v>-2.341056512000001</v>
+        <v>-2.400750336000001</v>
       </c>
       <c r="Q90">
-        <v>-0.2510565120000003</v>
+        <v>-0.3107503360000003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8018703849784632</v>
+        <v>0.8706040563401417</v>
       </c>
       <c r="T90">
-        <v>8.279280610563207</v>
+        <v>9.031942484250772</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1108687863284118</v>
+        <v>0.1096230696280925</v>
       </c>
       <c r="W90">
-        <v>0.1785375477052549</v>
+        <v>0.178787687618679</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5543439316420589</v>
+        <v>0.5481153481404626</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2548874881780399</v>
+        <v>0.2564374881780399</v>
       </c>
       <c r="C91">
-        <v>-13.74263113378968</v>
+        <v>-14.24057683783706</v>
       </c>
       <c r="D91">
-        <v>17.16976886621033</v>
+        <v>17.04342316216295</v>
       </c>
       <c r="E91">
-        <v>24.5124</v>
+        <v>24.884</v>
       </c>
       <c r="F91">
-        <v>33.0724</v>
+        <v>33.444</v>
       </c>
       <c r="G91">
         <v>2.16</v>
@@ -8743,37 +8743,37 @@
         <v>3.64</v>
       </c>
       <c r="M91">
-        <v>6.640937920000001</v>
+        <v>6.715555200000001</v>
       </c>
       <c r="N91">
-        <v>-3.000937920000001</v>
+        <v>-3.075555200000001</v>
       </c>
       <c r="O91">
-        <v>-0.6001875840000002</v>
+        <v>-0.6151110400000002</v>
       </c>
       <c r="P91">
-        <v>-2.400750336000001</v>
+        <v>-2.460444160000001</v>
       </c>
       <c r="Q91">
-        <v>-0.3107503360000003</v>
+        <v>-0.3704441600000004</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8706040563401417</v>
+        <v>0.9530844619741561</v>
       </c>
       <c r="T91">
-        <v>9.031942484250772</v>
+        <v>9.935136732675851</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1096230696280925</v>
+        <v>0.1084050355211137</v>
       </c>
       <c r="W91">
-        <v>0.178787687618679</v>
+        <v>0.1790322688673604</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5481153481404626</v>
+        <v>0.5420251776055687</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2564374881780399</v>
+        <v>0.25798748817804</v>
       </c>
       <c r="C92">
-        <v>-14.24057683783706</v>
+        <v>-14.73667666639993</v>
       </c>
       <c r="D92">
-        <v>17.04342316216295</v>
+        <v>16.91892333360007</v>
       </c>
       <c r="E92">
-        <v>24.884</v>
+        <v>25.2556</v>
       </c>
       <c r="F92">
-        <v>33.444</v>
+        <v>33.8156</v>
       </c>
       <c r="G92">
         <v>2.16</v>
@@ -8825,37 +8825,37 @@
         <v>3.64</v>
       </c>
       <c r="M92">
-        <v>6.715555200000001</v>
+        <v>6.790172480000001</v>
       </c>
       <c r="N92">
-        <v>-3.075555200000001</v>
+        <v>-3.150172480000001</v>
       </c>
       <c r="O92">
-        <v>-0.6151110400000002</v>
+        <v>-0.6300344960000002</v>
       </c>
       <c r="P92">
-        <v>-2.460444160000001</v>
+        <v>-2.520137984000001</v>
       </c>
       <c r="Q92">
-        <v>-0.3704441600000004</v>
+        <v>-0.4301379840000004</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9530844619741561</v>
+        <v>1.053893846637951</v>
       </c>
       <c r="T92">
-        <v>9.935136732675851</v>
+        <v>11.03904081408428</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1084050355211137</v>
+        <v>0.1072137713945081</v>
       </c>
       <c r="W92">
-        <v>0.1790322688673604</v>
+        <v>0.1792714747039828</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5420251776055687</v>
+        <v>0.5360688569725404</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.25798748817804</v>
+        <v>0.25953748817804</v>
       </c>
       <c r="C93">
-        <v>-14.73667666639993</v>
+        <v>-15.23097077771669</v>
       </c>
       <c r="D93">
-        <v>16.91892333360007</v>
+        <v>16.79622922228332</v>
       </c>
       <c r="E93">
-        <v>25.2556</v>
+        <v>25.6272</v>
       </c>
       <c r="F93">
-        <v>33.8156</v>
+        <v>34.1872</v>
       </c>
       <c r="G93">
         <v>2.16</v>
@@ -8907,37 +8907,37 @@
         <v>3.64</v>
       </c>
       <c r="M93">
-        <v>6.790172480000001</v>
+        <v>6.864789760000001</v>
       </c>
       <c r="N93">
-        <v>-3.150172480000001</v>
+        <v>-3.224789760000001</v>
       </c>
       <c r="O93">
-        <v>-0.6300344960000002</v>
+        <v>-0.6449579520000002</v>
       </c>
       <c r="P93">
-        <v>-2.520137984000001</v>
+        <v>-2.579831808000001</v>
       </c>
       <c r="Q93">
-        <v>-0.4301379840000004</v>
+        <v>-0.4898318080000004</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.053893846637951</v>
+        <v>1.179905577467696</v>
       </c>
       <c r="T93">
-        <v>11.03904081408428</v>
+        <v>12.41892091584482</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1072137713945081</v>
+        <v>0.106048404314133</v>
       </c>
       <c r="W93">
-        <v>0.1792714747039828</v>
+        <v>0.1795054804137221</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5360688569725404</v>
+        <v>0.5302420215706649</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.25953748817804</v>
+        <v>0.26108748817804</v>
       </c>
       <c r="C94">
-        <v>-15.23097077771669</v>
+        <v>-15.72349817352062</v>
       </c>
       <c r="D94">
-        <v>16.79622922228332</v>
+        <v>16.67530182647939</v>
       </c>
       <c r="E94">
-        <v>25.6272</v>
+        <v>25.9988</v>
       </c>
       <c r="F94">
-        <v>34.1872</v>
+        <v>34.55880000000001</v>
       </c>
       <c r="G94">
         <v>2.16</v>
@@ -8989,37 +8989,37 @@
         <v>3.64</v>
       </c>
       <c r="M94">
-        <v>6.864789760000001</v>
+        <v>6.939407040000002</v>
       </c>
       <c r="N94">
-        <v>-3.224789760000001</v>
+        <v>-3.299407040000002</v>
       </c>
       <c r="O94">
-        <v>-0.6449579520000002</v>
+        <v>-0.6598814080000004</v>
       </c>
       <c r="P94">
-        <v>-2.579831808000001</v>
+        <v>-2.639525632000001</v>
       </c>
       <c r="Q94">
-        <v>-0.4898318080000004</v>
+        <v>-0.5495256320000008</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.179905577467696</v>
+        <v>1.341920659963081</v>
       </c>
       <c r="T94">
-        <v>12.41892091584482</v>
+        <v>14.19305247525122</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.106048404314133</v>
+        <v>0.1049080988914004</v>
       </c>
       <c r="W94">
-        <v>0.1795054804137221</v>
+        <v>0.1797344537426068</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5302420215706649</v>
+        <v>0.5245404944570018</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.26108748817804</v>
+        <v>0.2626374881780399</v>
       </c>
       <c r="C95">
-        <v>-15.72349817352062</v>
+        <v>-16.21429674037462</v>
       </c>
       <c r="D95">
-        <v>16.67530182647939</v>
+        <v>16.55610325962539</v>
       </c>
       <c r="E95">
-        <v>25.9988</v>
+        <v>26.3704</v>
       </c>
       <c r="F95">
-        <v>34.55880000000001</v>
+        <v>34.93040000000001</v>
       </c>
       <c r="G95">
         <v>2.16</v>
@@ -9071,37 +9071,37 @@
         <v>3.64</v>
       </c>
       <c r="M95">
-        <v>6.939407040000002</v>
+        <v>7.014024320000002</v>
       </c>
       <c r="N95">
-        <v>-3.299407040000002</v>
+        <v>-3.374024320000002</v>
       </c>
       <c r="O95">
-        <v>-0.6598814080000004</v>
+        <v>-0.6748048640000004</v>
       </c>
       <c r="P95">
-        <v>-2.639525632000001</v>
+        <v>-2.699219456000001</v>
       </c>
       <c r="Q95">
-        <v>-0.5495256320000008</v>
+        <v>-0.6092194560000008</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.341920659963081</v>
+        <v>1.557940769956928</v>
       </c>
       <c r="T95">
-        <v>14.19305247525122</v>
+        <v>16.55856122112643</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1049080988914004</v>
+        <v>0.1037920552861727</v>
       </c>
       <c r="W95">
-        <v>0.1797344537426068</v>
+        <v>0.1799585552985365</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5245404944570018</v>
+        <v>0.5189602764308635</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2626374881780399</v>
+        <v>0.26418748817804</v>
       </c>
       <c r="C96">
-        <v>-16.21429674037462</v>
+        <v>-16.70340328924567</v>
       </c>
       <c r="D96">
-        <v>16.55610325962539</v>
+        <v>16.43859671075433</v>
       </c>
       <c r="E96">
-        <v>26.3704</v>
+        <v>26.742</v>
       </c>
       <c r="F96">
-        <v>34.93040000000001</v>
+        <v>35.30200000000001</v>
       </c>
       <c r="G96">
         <v>2.16</v>
@@ -9153,37 +9153,37 @@
         <v>3.64</v>
       </c>
       <c r="M96">
-        <v>7.014024320000002</v>
+        <v>7.088641600000002</v>
       </c>
       <c r="N96">
-        <v>-3.374024320000002</v>
+        <v>-3.448641600000002</v>
       </c>
       <c r="O96">
-        <v>-0.6748048640000004</v>
+        <v>-0.6897283200000004</v>
       </c>
       <c r="P96">
-        <v>-2.699219456000001</v>
+        <v>-2.758913280000001</v>
       </c>
       <c r="Q96">
-        <v>-0.6092194560000008</v>
+        <v>-0.6689132800000008</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.557940769956928</v>
+        <v>1.860368923948315</v>
       </c>
       <c r="T96">
-        <v>16.55856122112643</v>
+        <v>19.87027346535173</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1037920552861727</v>
+        <v>0.1026995073357919</v>
       </c>
       <c r="W96">
-        <v>0.1799585552985365</v>
+        <v>0.180177938926973</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5189602764308635</v>
+        <v>0.5134975366789596</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.26418748817804</v>
+        <v>0.2657374881780399</v>
       </c>
       <c r="C97">
-        <v>-16.70340328924567</v>
+        <v>-17.19085359340593</v>
       </c>
       <c r="D97">
-        <v>16.43859671075433</v>
+        <v>16.32274640659408</v>
       </c>
       <c r="E97">
-        <v>26.742</v>
+        <v>27.11360000000001</v>
       </c>
       <c r="F97">
-        <v>35.30200000000001</v>
+        <v>35.67360000000001</v>
       </c>
       <c r="G97">
         <v>2.16</v>
@@ -9235,37 +9235,37 @@
         <v>3.64</v>
       </c>
       <c r="M97">
-        <v>7.088641600000002</v>
+        <v>7.163258880000002</v>
       </c>
       <c r="N97">
-        <v>-3.448641600000002</v>
+        <v>-3.523258880000002</v>
       </c>
       <c r="O97">
-        <v>-0.6897283200000004</v>
+        <v>-0.7046517760000004</v>
       </c>
       <c r="P97">
-        <v>-2.758913280000001</v>
+        <v>-2.818607104000001</v>
       </c>
       <c r="Q97">
-        <v>-0.6689132800000008</v>
+        <v>-0.7286071040000008</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.860368923948315</v>
+        <v>2.314011154935394</v>
       </c>
       <c r="T97">
-        <v>19.87027346535173</v>
+        <v>24.83784183168967</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1026995073357919</v>
+        <v>0.1016297208010441</v>
       </c>
       <c r="W97">
-        <v>0.180177938926973</v>
+        <v>0.1803927520631503</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5134975366789596</v>
+        <v>0.5081486040052205</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2657374881780399</v>
+        <v>0.2672874881780399</v>
       </c>
       <c r="C98">
-        <v>-17.19085359340592</v>
+        <v>-17.67668242474236</v>
       </c>
       <c r="D98">
-        <v>16.32274640659408</v>
+        <v>16.20851757525764</v>
       </c>
       <c r="E98">
-        <v>27.1136</v>
+        <v>27.4852</v>
       </c>
       <c r="F98">
-        <v>35.6736</v>
+        <v>36.0452</v>
       </c>
       <c r="G98">
         <v>2.16</v>
@@ -9317,37 +9317,37 @@
         <v>3.64</v>
       </c>
       <c r="M98">
-        <v>7.16325888</v>
+        <v>7.237876160000001</v>
       </c>
       <c r="N98">
-        <v>-3.52325888</v>
+        <v>-3.597876160000001</v>
       </c>
       <c r="O98">
-        <v>-0.704651776</v>
+        <v>-0.7195752320000002</v>
       </c>
       <c r="P98">
-        <v>-2.818607104</v>
+        <v>-2.878300928000001</v>
       </c>
       <c r="Q98">
-        <v>-0.7286071039999995</v>
+        <v>-0.7883009280000004</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.314011154935388</v>
+        <v>3.07008153991385</v>
       </c>
       <c r="T98">
-        <v>24.8378418316896</v>
+        <v>33.1171224422528</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1016297208010441</v>
+        <v>0.100581991720621</v>
       </c>
       <c r="W98">
-        <v>0.1803927520631503</v>
+        <v>0.1806031360624993</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5081486040052205</v>
+        <v>0.5029099586031049</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2672874881780399</v>
+        <v>0.3045934283411822</v>
       </c>
       <c r="C99">
-        <v>-17.67668242474236</v>
+        <v>-20.38479456367746</v>
       </c>
       <c r="D99">
-        <v>16.20851757525764</v>
+        <v>13.87200543632254</v>
       </c>
       <c r="E99">
-        <v>27.4852</v>
+        <v>27.8568</v>
       </c>
       <c r="F99">
-        <v>36.0452</v>
+        <v>36.4168</v>
       </c>
       <c r="G99">
         <v>2.16</v>
@@ -9399,45 +9399,45 @@
         <v>3.64</v>
       </c>
       <c r="M99">
-        <v>7.237876160000001</v>
+        <v>8.58708144</v>
       </c>
       <c r="N99">
-        <v>-3.597876160000001</v>
+        <v>-4.94708144</v>
       </c>
       <c r="O99">
-        <v>-0.7195752320000002</v>
+        <v>-0.989416288</v>
       </c>
       <c r="P99">
-        <v>-2.878300928000001</v>
+        <v>-3.957665152</v>
       </c>
       <c r="Q99">
-        <v>-0.7883009280000004</v>
+        <v>-1.867665151999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.07008153991385</v>
+        <v>4.655019318027891</v>
       </c>
       <c r="T99">
-        <v>33.1171224422528</v>
+        <v>50.47284074044073</v>
       </c>
       <c r="U99">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.100581991720621</v>
+        <v>0.08477851352484669</v>
       </c>
       <c r="W99">
-        <v>0.1806031360624993</v>
+        <v>0.2158092265108412</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.5029099586031049</v>
+        <v>0.4238925676242336</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3045934283411822</v>
+        <v>0.3064934283411823</v>
       </c>
       <c r="C100">
-        <v>-20.38479456367746</v>
+        <v>-20.8574972669436</v>
       </c>
       <c r="D100">
-        <v>13.87200543632254</v>
+        <v>13.7709027330564</v>
       </c>
       <c r="E100">
-        <v>27.8568</v>
+        <v>28.2284</v>
       </c>
       <c r="F100">
-        <v>36.4168</v>
+        <v>36.7884</v>
       </c>
       <c r="G100">
         <v>2.16</v>
@@ -9481,37 +9481,37 @@
         <v>3.64</v>
       </c>
       <c r="M100">
-        <v>8.58708144</v>
+        <v>8.674704720000001</v>
       </c>
       <c r="N100">
-        <v>-4.94708144</v>
+        <v>-5.034704720000001</v>
       </c>
       <c r="O100">
-        <v>-0.989416288</v>
+        <v>-1.006940944</v>
       </c>
       <c r="P100">
-        <v>-3.957665152</v>
+        <v>-4.027763776</v>
       </c>
       <c r="Q100">
-        <v>-1.867665151999999</v>
+        <v>-1.937763776</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.655019318027891</v>
+        <v>9.264238636055783</v>
       </c>
       <c r="T100">
-        <v>50.47284074044073</v>
+        <v>100.9456814808815</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08477851352484669</v>
+        <v>0.0839221649033836</v>
       </c>
       <c r="W100">
-        <v>0.2158092265108412</v>
+        <v>0.2160111535157822</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4238925676242336</v>
+        <v>0.419610824516918</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3064934283411823</v>
-      </c>
-      <c r="C101">
-        <v>-20.8574972669436</v>
-      </c>
-      <c r="D101">
-        <v>13.7709027330564</v>
-      </c>
-      <c r="E101">
-        <v>28.2284</v>
-      </c>
-      <c r="F101">
-        <v>36.7884</v>
-      </c>
-      <c r="G101">
-        <v>2.16</v>
-      </c>
-      <c r="H101">
-        <v>28.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.73</v>
-      </c>
-      <c r="K101">
-        <v>2.09</v>
-      </c>
-      <c r="L101">
-        <v>3.64</v>
-      </c>
-      <c r="M101">
-        <v>8.674704720000001</v>
-      </c>
-      <c r="N101">
-        <v>-5.034704720000001</v>
-      </c>
-      <c r="O101">
-        <v>-1.006940944</v>
-      </c>
-      <c r="P101">
-        <v>-4.027763776</v>
-      </c>
-      <c r="Q101">
-        <v>-1.937763776</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.264238636055783</v>
-      </c>
-      <c r="T101">
-        <v>100.9456814808815</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0839221649033836</v>
-      </c>
-      <c r="W101">
-        <v>0.2160111535157822</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.419610824516918</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
